--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,417 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E7" s="2">
         <v>45198</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44925</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44743</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44652</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44470</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44379</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44288</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44197</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44099</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44008</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43917</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43826</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43644</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43553</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43462</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43371</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43280</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43189</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43098</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43007</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42734</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E8" s="3">
         <v>75900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>77100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>71200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>70100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>72000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>70200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>63500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>59300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>52800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>69100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>72700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>73500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>67200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>63700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>73700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>74500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>71100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>60100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>71500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>73600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>71400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>70100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E9" s="3">
         <v>45600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>44500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>43900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>45700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>41200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>38900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>47100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>45400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>48300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>47500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>44600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>49600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>49200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>48300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>38600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>47800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>49200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>48300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>45600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E10" s="3">
         <v>30300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>29600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>28100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>30000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>27800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>29800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>24100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>23100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>24500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,37 +1299,40 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-500</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1321,62 +1340,65 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>5500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>4400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-1100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>100</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1407,8 +1429,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
@@ -1425,11 +1447,11 @@
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T15" s="3">
         <v>200</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>8</v>
@@ -1443,8 +1465,8 @@
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1467,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E17" s="3">
         <v>62100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>64300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>60000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>56500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>58000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>61700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>62300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>60500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>59000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>57800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>61800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>65500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>58600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>60100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>65500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>60300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>62800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>53700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>63600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>67100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>63500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>60400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E18" s="3">
         <v>13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>14200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1808,118 +1841,124 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
         <v>14600</v>
       </c>
-      <c r="E21" s="3">
-        <v>13600</v>
-      </c>
       <c r="F21" s="3">
-        <v>12100</v>
+        <v>14400</v>
       </c>
       <c r="G21" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H21" s="3">
         <v>14400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14900</v>
       </c>
-      <c r="I21" s="3">
-        <v>15000</v>
-      </c>
       <c r="J21" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K21" s="3">
         <v>14400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>900</v>
       </c>
       <c r="F22" s="3">
         <v>900</v>
       </c>
       <c r="G22" s="3">
+        <v>900</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
@@ -1954,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
@@ -1966,7 +2005,7 @@
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
@@ -1981,7 +2020,7 @@
         <v>200</v>
       </c>
       <c r="AC22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD22" s="3">
         <v>100</v>
@@ -1992,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E23" s="3">
         <v>12900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>9600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
-      </c>
-      <c r="X24" s="3">
-        <v>2400</v>
       </c>
       <c r="Y24" s="3">
         <v>2400</v>
       </c>
       <c r="Z24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA24" s="3">
         <v>800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1600</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>3300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E26" s="3">
         <v>9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6900</v>
-      </c>
-      <c r="U26" s="3">
-        <v>7000</v>
       </c>
       <c r="V26" s="3">
         <v>7000</v>
       </c>
       <c r="W26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X26" s="3">
         <v>3300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E27" s="3">
         <v>9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6900</v>
-      </c>
-      <c r="U27" s="3">
-        <v>7000</v>
       </c>
       <c r="V27" s="3">
         <v>7000</v>
       </c>
       <c r="W27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X27" s="3">
         <v>3300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,13 +2601,16 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>8</v>
@@ -2558,8 +2618,8 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2586,11 +2646,11 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -2601,28 +2661,28 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-3500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>5800</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2636,8 +2696,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2912,100 +2981,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E33" s="3">
         <v>9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E35" s="3">
         <v>9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E38" s="2">
         <v>45198</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44925</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44743</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44652</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44470</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44379</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44288</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44197</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44099</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44008</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43917</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43826</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43644</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43553</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43462</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43371</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43280</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43189</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43098</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43007</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42734</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,8 +3438,9 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3380,73 +3466,76 @@
         <v>47800</v>
       </c>
       <c r="K41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="L41" s="3">
         <v>45800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>49500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>37400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>17500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>14400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>17100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>19700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,8 +3626,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3564,73 +3656,76 @@
         <v>50500</v>
       </c>
       <c r="K43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="L43" s="3">
         <v>50600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>49600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>47200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>38500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>32800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>36200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>53400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>49800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>57900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>56000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>54800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>56900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>56800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>51900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>52300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>55600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>50400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>49900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>47400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3721,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3748,73 +3846,76 @@
         <v>5400</v>
       </c>
       <c r="K45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L45" s="3">
         <v>5800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3840,73 +3941,76 @@
         <v>103600</v>
       </c>
       <c r="K46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="L46" s="3">
         <v>102200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>105700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>102300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>92400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>84800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>82700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>78100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>80000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>78600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>78000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>75300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>70700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>73100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>73800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>73300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>79100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>75300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>74700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>68000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>69600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>68800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3997,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4024,73 +4131,76 @@
         <v>19600</v>
       </c>
       <c r="K48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="L48" s="3">
         <v>19700</v>
       </c>
       <c r="M48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="N48" s="3">
         <v>19900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>28700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>28900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4116,73 +4226,76 @@
         <v>84600</v>
       </c>
       <c r="K49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="L49" s="3">
         <v>85100</v>
       </c>
       <c r="M49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="N49" s="3">
         <v>85400</v>
       </c>
       <c r="O49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="P49" s="3">
         <v>85300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>83900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>83800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>83800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>84200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>84600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>84200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>84600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>85700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>85100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>85000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>85300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>72600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>72400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4392,73 +4511,76 @@
         <v>500</v>
       </c>
       <c r="K52" s="3">
+        <v>500</v>
+      </c>
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,8 +4671,11 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4576,73 +4701,76 @@
         <v>208400</v>
       </c>
       <c r="K54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="L54" s="3">
         <v>207500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>211400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>208800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>199400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>192500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>196100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>192500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>195100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>193700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>193900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>191400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>187700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>180800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>187100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>185900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>191000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>185200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>182200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>174900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>160800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>159300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,8 +4838,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4736,73 +4866,76 @@
         <v>8000</v>
       </c>
       <c r="K57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L57" s="3">
         <v>7700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4893,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4920,73 +5056,76 @@
         <v>39900</v>
       </c>
       <c r="K59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="L59" s="3">
         <v>47200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>49900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>50900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>41200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>36500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>37500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>30500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>35500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>30200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>36800</v>
-      </c>
-      <c r="X59" s="3">
-        <v>34100</v>
       </c>
       <c r="Y59" s="3">
         <v>34100</v>
       </c>
       <c r="Z59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AA59" s="3">
         <v>39800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>43000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>36000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>37100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>34200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>46700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5012,73 +5151,76 @@
         <v>48000</v>
       </c>
       <c r="K60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="L60" s="3">
         <v>54900</v>
       </c>
       <c r="M60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="N60" s="3">
         <v>55600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>42600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>42300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>42300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>36600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>44200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>39200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>42500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>48400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>51400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>44600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>45200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>45800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>55800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5131,46 +5273,49 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>2500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13500</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>19000</v>
       </c>
       <c r="AA61" s="3">
         <v>19000</v>
       </c>
       <c r="AB61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>22000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5196,73 +5341,76 @@
         <v>10200</v>
       </c>
       <c r="K62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="L62" s="3">
         <v>8800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>17500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>17800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,8 +5691,11 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5564,73 +5721,76 @@
         <v>58100</v>
       </c>
       <c r="K66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="L66" s="3">
         <v>63700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>64400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>57500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>54300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>60200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>57900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>57200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>58700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>64300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>75700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>78000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>84100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>83100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>64700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>73000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,8 +6201,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6058,73 +6231,76 @@
         <v>18300</v>
       </c>
       <c r="K72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="L72" s="3">
         <v>11300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-15200</v>
       </c>
       <c r="Q72" s="3">
         <v>-15200</v>
       </c>
       <c r="R72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="S72" s="3">
         <v>-8200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-13700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-25400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-19900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,8 +6581,11 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6426,73 +6611,76 @@
         <v>150300</v>
       </c>
       <c r="K76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="L76" s="3">
         <v>143900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>148500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>144400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>143200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>140900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>138600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>136600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>140800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>137600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>138700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>131200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>129700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>123600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>128400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>121600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>115400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>107300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>98100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>91800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>96000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>86300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E80" s="2">
         <v>45198</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44925</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44743</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44652</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44470</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44379</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44288</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44197</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44099</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44008</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43917</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43826</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43644</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43553</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43462</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43371</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43280</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43189</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43098</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43007</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42734</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E81" s="3">
         <v>9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,22 +7003,23 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>900</v>
       </c>
-      <c r="E83" s="3">
-        <v>800</v>
-      </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>-2600</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -6830,13 +7028,13 @@
         <v>800</v>
       </c>
       <c r="J83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K83" s="3">
         <v>900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1100</v>
       </c>
       <c r="M83" s="3">
         <v>1100</v>
@@ -6845,19 +7043,19 @@
         <v>1100</v>
       </c>
       <c r="O83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="P83" s="3">
         <v>1200</v>
       </c>
       <c r="Q83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1100</v>
       </c>
       <c r="T83" s="3">
         <v>1100</v>
@@ -6866,10 +7064,10 @@
         <v>1100</v>
       </c>
       <c r="V83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W83" s="3">
         <v>900</v>
-      </c>
-      <c r="W83" s="3">
-        <v>1200</v>
       </c>
       <c r="X83" s="3">
         <v>1200</v>
@@ -6884,22 +7082,25 @@
         <v>1200</v>
       </c>
       <c r="AB83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AC83" s="3">
         <v>1100</v>
       </c>
       <c r="AD83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>900</v>
       </c>
       <c r="AF83" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>7200</v>
       </c>
-      <c r="E89" s="3">
-        <v>7700</v>
-      </c>
       <c r="F89" s="3">
-        <v>-3100</v>
+        <v>4700</v>
       </c>
       <c r="G89" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="H89" s="3">
         <v>24800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9800</v>
       </c>
-      <c r="I89" s="3">
-        <v>18200</v>
-      </c>
       <c r="J89" s="3">
+        <v>24300</v>
+      </c>
+      <c r="K89" s="3">
         <v>6100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>15800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>12100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7514,70 +7734,73 @@
         <v>-1000</v>
       </c>
       <c r="L91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-1100</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
         <v>-1100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1100</v>
+        <v>-2100</v>
       </c>
       <c r="G94" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
-        <v>-1300</v>
-      </c>
       <c r="J94" s="3">
-        <v>-1000</v>
+        <v>-2300</v>
       </c>
       <c r="K94" s="3">
         <v>-1000</v>
       </c>
       <c r="L94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,100 +8118,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>-3000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3000</v>
+        <v>-6000</v>
       </c>
       <c r="G96" s="3">
-        <v>-3500</v>
+        <v>7400</v>
       </c>
       <c r="H96" s="3">
         <v>-3500</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-6400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-6100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-5800</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-5800</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-5400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,105 +8496,111 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12100</v>
       </c>
-      <c r="E100" s="3">
-        <v>-7700</v>
-      </c>
       <c r="F100" s="3">
-        <v>-9200</v>
+        <v>-16900</v>
       </c>
       <c r="G100" s="3">
+        <v>60500</v>
+      </c>
+      <c r="H100" s="3">
         <v>-60100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3500</v>
       </c>
-      <c r="I100" s="3">
-        <v>-3000</v>
-      </c>
       <c r="J100" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-26000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -8394,35 +8642,35 @@
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -8438,96 +8686,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6000</v>
       </c>
-      <c r="E102" s="3">
-        <v>-1000</v>
-      </c>
       <c r="F102" s="3">
-        <v>-13400</v>
+        <v>-14400</v>
       </c>
       <c r="G102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-36800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5400</v>
       </c>
-      <c r="I102" s="3">
-        <v>13900</v>
-      </c>
       <c r="J102" s="3">
+        <v>15900</v>
+      </c>
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E7" s="2">
         <v>45289</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45198</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44925</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44743</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44652</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44470</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44379</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44288</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44197</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44099</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44008</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43917</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43826</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43735</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43644</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43553</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43462</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43371</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43280</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43189</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43098</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43007</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42734</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E8" s="3">
         <v>72400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>75900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>77100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>70100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>72000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>75700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>70200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>71900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>73200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>63500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>59300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>57900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>52800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>69500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>69100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>72700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>73500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>67200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>63700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>73700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>74500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>71100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>60100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>71500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>73600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>71400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>70100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E9" s="3">
         <v>43100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>44500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>43900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>42700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>41200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>38900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>45400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>48300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>47500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>44600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>40100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>49600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>49200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>48300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>38600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>47800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>49200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>48300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>45600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E10" s="3">
         <v>29300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>29600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>29800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>24100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>25300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>21500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>23100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>24500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,40 +1319,43 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-500</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1343,62 +1363,65 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>5500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>5000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>4400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-1100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>100</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1432,8 +1455,8 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
@@ -1450,11 +1473,11 @@
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" s="3">
         <v>200</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
@@ -1468,8 +1491,8 @@
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,103 +1550,107 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E17" s="3">
         <v>60900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>62100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>64300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>60000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>58000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>61700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>62300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>58200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>60500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>57800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>61800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>65500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>58600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>60100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>65500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>60300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>62800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>53700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>63600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>67100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>63500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>60400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,94 +1658,97 @@
         <v>11500</v>
       </c>
       <c r="E18" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F18" s="3">
         <v>13800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1782,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1844,124 +1878,130 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>12500</v>
       </c>
       <c r="E21" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F21" s="3">
         <v>14600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>13600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>12100</v>
+      </c>
+      <c r="I21" s="3">
         <v>14400</v>
       </c>
-      <c r="G21" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>16000</v>
+      </c>
+      <c r="L21" s="3">
         <v>14400</v>
       </c>
-      <c r="I21" s="3">
-        <v>14900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>16000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>14400</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>15500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>900</v>
       </c>
       <c r="G22" s="3">
         <v>900</v>
       </c>
       <c r="H22" s="3">
+        <v>900</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
@@ -1996,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
@@ -2008,7 +2048,7 @@
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>200</v>
@@ -2023,7 +2063,7 @@
         <v>200</v>
       </c>
       <c r="AD22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE22" s="3">
         <v>100</v>
@@ -2034,198 +2074,207 @@
       <c r="AG22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E23" s="3">
         <v>10800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>14100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>2400</v>
       </c>
       <c r="Z24" s="3">
         <v>2400</v>
       </c>
       <c r="AA24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB24" s="3">
         <v>800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1600</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>3300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E26" s="3">
         <v>7900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6900</v>
-      </c>
-      <c r="V26" s="3">
-        <v>7000</v>
       </c>
       <c r="W26" s="3">
         <v>7000</v>
       </c>
       <c r="X26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y26" s="3">
         <v>3300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E27" s="3">
         <v>7900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6900</v>
-      </c>
-      <c r="V27" s="3">
-        <v>7000</v>
       </c>
       <c r="W27" s="3">
         <v>7000</v>
       </c>
       <c r="X27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y27" s="3">
         <v>3300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,16 +2662,19 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -2621,8 +2682,8 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2649,11 +2710,11 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2664,28 +2725,28 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>5800</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2956,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2984,103 +3054,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E33" s="3">
         <v>7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E35" s="3">
         <v>7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E38" s="2">
         <v>45289</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45198</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44925</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44743</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44652</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44470</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44379</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44288</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44197</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44099</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44008</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43917</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43826</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43735</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43644</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43553</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43462</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43371</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43280</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43189</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43098</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43007</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42734</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3525,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F41" s="3">
         <v>9900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>30300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>67000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>61700</v>
-      </c>
-      <c r="J41" s="3">
-        <v>47800</v>
       </c>
       <c r="K41" s="3">
         <v>47800</v>
       </c>
       <c r="L41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="M41" s="3">
         <v>45800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>51100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>37400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>23700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>17500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>14400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>17100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>19700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,103 +3719,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>52100</v>
+      </c>
+      <c r="F43" s="3">
         <v>62200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>57800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>52000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>48400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>52100</v>
-      </c>
-      <c r="I43" s="3">
-        <v>49500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>50500</v>
       </c>
       <c r="K43" s="3">
         <v>50500</v>
       </c>
       <c r="L43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="M43" s="3">
         <v>50600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>49600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>47200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>38500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>32800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>36200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>53400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>57900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>54500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>56000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>54800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>56900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>56800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>51900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>52300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>55600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>50400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>49900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>47400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,198 +3915,207 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="E45" s="3">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="F45" s="3">
         <v>3200</v>
       </c>
       <c r="G45" s="3">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="H45" s="3">
         <v>3200</v>
       </c>
       <c r="I45" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J45" s="3">
-        <v>5400</v>
+        <v>3200</v>
       </c>
       <c r="K45" s="3">
         <v>5400</v>
       </c>
       <c r="L45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>75400</v>
+      </c>
+      <c r="F46" s="3">
         <v>75300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>76800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>72000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>81200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>122400</v>
-      </c>
-      <c r="I46" s="3">
-        <v>114200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>103600</v>
       </c>
       <c r="K46" s="3">
         <v>103600</v>
       </c>
       <c r="L46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="M46" s="3">
         <v>102200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>105700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>102300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>92400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>84800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>82700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>78100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>80000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>78600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>78000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>75300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>70700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>73100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>73800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>73300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>79100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>75300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>74700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>68000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>69600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>68800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,198 +4209,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F48" s="3">
         <v>21600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>21700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>21500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>20100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>19500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>19700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>19600</v>
       </c>
       <c r="K48" s="3">
         <v>19600</v>
       </c>
       <c r="L48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="M48" s="3">
         <v>19700</v>
       </c>
       <c r="N48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="O48" s="3">
         <v>19900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>29100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>28700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>28900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>24300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>22800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>84200</v>
+      </c>
+      <c r="F49" s="3">
         <v>83700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>84100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>83800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>83500</v>
-      </c>
-      <c r="H49" s="3">
-        <v>82500</v>
       </c>
       <c r="I49" s="3">
         <v>83500</v>
       </c>
       <c r="J49" s="3">
-        <v>84600</v>
+        <v>82500</v>
       </c>
       <c r="K49" s="3">
         <v>84600</v>
       </c>
       <c r="L49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="M49" s="3">
         <v>85100</v>
       </c>
       <c r="N49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="O49" s="3">
         <v>85400</v>
       </c>
       <c r="P49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="Q49" s="3">
         <v>85300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>83900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>83800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>84600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>83800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>84200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>84600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>84200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>84700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>85700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>85100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>85000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>85300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>72600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>72400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4505,82 +4625,85 @@
         <v>300</v>
       </c>
       <c r="I52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>
       </c>
       <c r="L52" s="3">
+        <v>500</v>
+      </c>
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>179300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>181400</v>
+      </c>
+      <c r="F54" s="3">
         <v>180800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>182900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>177700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>185000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>224700</v>
-      </c>
-      <c r="I54" s="3">
-        <v>217900</v>
-      </c>
-      <c r="J54" s="3">
-        <v>208400</v>
       </c>
       <c r="K54" s="3">
         <v>208400</v>
       </c>
       <c r="L54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="M54" s="3">
         <v>207500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>211400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>208800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>199400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>192500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>196100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>192500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>195100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>193700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>193900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>191400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>187700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>180800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>187100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>185900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>191000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>185200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>182200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>174900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>160800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>159300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,103 +4969,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F57" s="3">
         <v>5000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>8000</v>
       </c>
       <c r="K57" s="3">
         <v>8000</v>
       </c>
       <c r="L57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M57" s="3">
         <v>7700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,219 +5163,228 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>42300</v>
+      </c>
+      <c r="F59" s="3">
         <v>41900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>41400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>39400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>50900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>47300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>46200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>39900</v>
       </c>
       <c r="K59" s="3">
         <v>39900</v>
       </c>
       <c r="L59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="M59" s="3">
         <v>47200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>50900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>36500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>37500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>30500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>35200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>35500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>30200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>36800</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>34100</v>
       </c>
       <c r="Z59" s="3">
         <v>34100</v>
       </c>
       <c r="AA59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AB59" s="3">
         <v>39800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>43000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>36000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>37100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>34200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>46700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>49900</v>
+      </c>
+      <c r="F60" s="3">
         <v>47000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>46900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>46300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>59600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>51900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>51600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>48000</v>
       </c>
       <c r="K60" s="3">
         <v>48000</v>
       </c>
       <c r="L60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="M60" s="3">
         <v>54900</v>
       </c>
       <c r="N60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="O60" s="3">
         <v>55600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>42600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>45100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>42300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>42300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>36600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>44200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>42500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>48400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>51400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>44600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>45200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>45800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>55800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>32700</v>
+      </c>
+      <c r="F61" s="3">
         <v>43700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>52700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>57700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>59700</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -5276,141 +5419,147 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>2500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>19000</v>
       </c>
       <c r="AB61" s="3">
         <v>19000</v>
       </c>
       <c r="AC61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>22000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F62" s="3">
         <v>9300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>10500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>10300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>7500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>8600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>9400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>10200</v>
       </c>
       <c r="K62" s="3">
         <v>10200</v>
       </c>
       <c r="L62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="M62" s="3">
         <v>8800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>17500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>91300</v>
+      </c>
+      <c r="F66" s="3">
         <v>100000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>110000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>114200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>126700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>60600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>61100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>58100</v>
       </c>
       <c r="K66" s="3">
         <v>58100</v>
       </c>
       <c r="L66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="M66" s="3">
         <v>63700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>57500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>54300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>60200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>57900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>58700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>64300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>75700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>78000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>84100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>83100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>73000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>60800</v>
+      </c>
+      <c r="F72" s="3">
         <v>56000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>49500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>43800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>38600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>31900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>25000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>18300</v>
       </c>
       <c r="K72" s="3">
         <v>18300</v>
       </c>
       <c r="L72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="M72" s="3">
         <v>11300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-15200</v>
       </c>
       <c r="R72" s="3">
         <v>-15200</v>
       </c>
       <c r="S72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="T72" s="3">
         <v>-8200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-13700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-17100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-18300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-25400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>90100</v>
+      </c>
+      <c r="F76" s="3">
         <v>80800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>72900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>63400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>58300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>164100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>156800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>150300</v>
       </c>
       <c r="K76" s="3">
         <v>150300</v>
       </c>
       <c r="L76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="M76" s="3">
         <v>143900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>148500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>144400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>143200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>140900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>138600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>136600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>140800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>137600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>138700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>131200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>129700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>123600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>128400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>121600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>115400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>107300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>98100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>91800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>96000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>86300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E80" s="2">
         <v>45289</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45198</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44925</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44743</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44652</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44470</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44379</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44288</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44197</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44099</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44008</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43917</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43826</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43735</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43644</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43553</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43462</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43371</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43280</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43189</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43098</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43007</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42734</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E81" s="3">
         <v>7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,22 +7202,23 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>-2600</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -7028,16 +7227,16 @@
         <v>800</v>
       </c>
       <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>1800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1100</v>
       </c>
       <c r="N83" s="3">
         <v>1100</v>
@@ -7046,19 +7245,19 @@
         <v>1100</v>
       </c>
       <c r="P83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Q83" s="3">
         <v>1200</v>
       </c>
       <c r="R83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S83" s="3">
         <v>1100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1100</v>
       </c>
       <c r="U83" s="3">
         <v>1100</v>
@@ -7067,10 +7266,10 @@
         <v>1100</v>
       </c>
       <c r="W83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X83" s="3">
         <v>900</v>
-      </c>
-      <c r="X83" s="3">
-        <v>1200</v>
       </c>
       <c r="Y83" s="3">
         <v>1200</v>
@@ -7085,22 +7284,25 @@
         <v>1200</v>
       </c>
       <c r="AC83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AD83" s="3">
         <v>1100</v>
       </c>
       <c r="AE83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>900</v>
       </c>
       <c r="AG83" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>2800</v>
       </c>
       <c r="E89" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F89" s="3">
         <v>7200</v>
       </c>
-      <c r="F89" s="3">
-        <v>4700</v>
-      </c>
       <c r="G89" s="3">
-        <v>-62000</v>
+        <v>7700</v>
       </c>
       <c r="H89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I89" s="3">
         <v>24800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>11300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>17200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>12100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,31 +7924,32 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="E91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="F91" s="3">
         <v>-1100</v>
       </c>
       <c r="G91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-1000</v>
       </c>
       <c r="K91" s="3">
         <v>-1000</v>
@@ -7737,70 +7958,73 @@
         <v>-1000</v>
       </c>
       <c r="M91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-900</v>
       </c>
       <c r="E94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
-        <v>-2100</v>
-      </c>
       <c r="G94" s="3">
-        <v>3600</v>
+        <v>-1100</v>
       </c>
       <c r="H94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-1000</v>
       </c>
       <c r="L94" s="3">
         <v>-1000</v>
       </c>
       <c r="M94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,25 +8352,26 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="E96" s="3">
         <v>-3000</v>
       </c>
       <c r="F96" s="3">
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
       <c r="G96" s="3">
-        <v>7400</v>
+        <v>-3000</v>
       </c>
       <c r="H96" s="3">
-        <v>-3500</v>
+        <v>-3000</v>
       </c>
       <c r="I96" s="3">
         <v>-3500</v>
@@ -8146,76 +8380,79 @@
         <v>-3500</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-6400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-5800</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-5400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,108 +8742,114 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-9800</v>
       </c>
       <c r="E100" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-12100</v>
       </c>
-      <c r="F100" s="3">
-        <v>-16900</v>
-      </c>
       <c r="G100" s="3">
-        <v>60500</v>
+        <v>-7700</v>
       </c>
       <c r="H100" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-60100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-26000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -8645,35 +8894,35 @@
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>-8000</v>
       </c>
       <c r="E102" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-6000</v>
       </c>
-      <c r="F102" s="3">
-        <v>-14400</v>
-      </c>
       <c r="G102" s="3">
-        <v>2100</v>
+        <v>-1000</v>
       </c>
       <c r="H102" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="I102" s="3">
         <v>-36800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,246 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E7" s="2">
         <v>45380</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45289</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45198</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44925</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44743</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44652</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44470</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44379</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44288</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44197</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44099</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44008</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43917</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43826</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43735</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43644</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43553</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43462</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43371</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43280</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43189</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43098</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43007</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42734</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E8" s="3">
         <v>77200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>72400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>77100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>70100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>72000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>75900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>75700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>70200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>73200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>63500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>59300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>57900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>52800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>69500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>69100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>72700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>73500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>67200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>63700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>73700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>74500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>71100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>60100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>71500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>73600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>71400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>70100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -903,195 +910,201 @@
         <v>47200</v>
       </c>
       <c r="E9" s="3">
+        <v>47200</v>
+      </c>
+      <c r="F9" s="3">
         <v>43100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>46900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>44500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>40500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>45900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>42700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>43400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>41200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>38900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>39700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>40700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>47100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>45400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>48300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>47500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>44600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>40100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>49600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>49200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>48300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>38600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>47800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>49200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>48300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>45600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E10" s="3">
         <v>30000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>29600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>29800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>18200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>24400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>24100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>25300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>22800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>21500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>23700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>24400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>23100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>24500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1139,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1224,8 +1238,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,43 +1339,46 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-500</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1366,62 +1386,65 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>5500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>5000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>4400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>100</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1458,8 +1481,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>8</v>
@@ -1476,11 +1499,11 @@
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3">
         <v>200</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
@@ -1494,8 +1517,8 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E17" s="3">
         <v>65700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>60900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>62100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>64300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>60000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>56500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>61700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>62300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>58200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>60500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>59000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>57800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>53400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>61800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>65500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>58600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>60100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>65500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>60300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>62800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>53700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>63600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>67100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>63500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>60400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11500</v>
+        <v>12600</v>
       </c>
       <c r="E18" s="3">
         <v>11500</v>
       </c>
       <c r="F18" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G18" s="3">
         <v>13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,8 +1816,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1881,106 +1915,112 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E21" s="3">
         <v>12500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1988,23 +2028,23 @@
         <v>500</v>
       </c>
       <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>900</v>
       </c>
       <c r="H22" s="3">
         <v>900</v>
       </c>
       <c r="I22" s="3">
+        <v>900</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -2039,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
@@ -2051,7 +2091,7 @@
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>200</v>
@@ -2066,7 +2106,7 @@
         <v>200</v>
       </c>
       <c r="AE22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF22" s="3">
         <v>100</v>
@@ -2077,204 +2117,213 @@
       <c r="AH22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E23" s="3">
         <v>11100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>14100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>2400</v>
       </c>
       <c r="AA24" s="3">
         <v>2400</v>
       </c>
       <c r="AB24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC24" s="3">
         <v>800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1600</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>3300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,8 +2420,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2380,97 +2432,100 @@
         <v>8700</v>
       </c>
       <c r="E26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F26" s="3">
         <v>7900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6900</v>
-      </c>
-      <c r="W26" s="3">
-        <v>7000</v>
       </c>
       <c r="X26" s="3">
         <v>7000</v>
       </c>
       <c r="Y26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z26" s="3">
         <v>3300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>11700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2478,97 +2533,100 @@
         <v>8700</v>
       </c>
       <c r="E27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F27" s="3">
         <v>7900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6900</v>
-      </c>
-      <c r="W27" s="3">
-        <v>7000</v>
       </c>
       <c r="X27" s="3">
         <v>7000</v>
       </c>
       <c r="Y27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z27" s="3">
         <v>3300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>11700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,25 +2723,28 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2713,11 +2774,11 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-200</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
@@ -2728,28 +2789,28 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>5800</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,8 +3026,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3057,8 +3127,11 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3066,97 +3139,100 @@
         <v>8700</v>
       </c>
       <c r="E33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F33" s="3">
         <v>7900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>11500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,8 +3329,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3262,200 +3341,206 @@
         <v>8700</v>
       </c>
       <c r="E35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F35" s="3">
         <v>7900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>11500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E38" s="2">
         <v>45380</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45289</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45198</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44925</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44743</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44652</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44470</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44379</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44288</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44197</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44099</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44008</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43917</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43826</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43735</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43644</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43553</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43462</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43371</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43280</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43189</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43098</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43007</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42734</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,106 +3612,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E41" s="3">
         <v>13000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>67000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>47800</v>
       </c>
       <c r="L41" s="3">
         <v>47800</v>
       </c>
       <c r="M41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="N41" s="3">
         <v>45800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>51100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>49500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>37400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>23700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>17500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>14400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>17100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>19700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,106 +3812,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E43" s="3">
         <v>58000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>52100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>62200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>57800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>52000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>50500</v>
       </c>
       <c r="L43" s="3">
         <v>50500</v>
       </c>
       <c r="M43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="N43" s="3">
         <v>50600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>47200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>38500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>32800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>36200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>37000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>53400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>49800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>57900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>54500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>56000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>54800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>56900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>56800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>51900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>52300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>55600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>50400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>49900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>47400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3918,19 +4014,22 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3200</v>
       </c>
       <c r="G45" s="3">
         <v>3200</v>
@@ -3939,183 +4038,189 @@
         <v>3200</v>
       </c>
       <c r="I45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>5400</v>
       </c>
       <c r="L45" s="3">
         <v>5400</v>
       </c>
       <c r="M45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E46" s="3">
         <v>73700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>75400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>76800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>72000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>81200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>122400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>103600</v>
       </c>
       <c r="L46" s="3">
         <v>103600</v>
       </c>
       <c r="M46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="N46" s="3">
         <v>102200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>105700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>102300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>92400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>84800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>82700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>78100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>80000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>78600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>78000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>75300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>70700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>73100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>73800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>73300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>79100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>75300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>74700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>68000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>69600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>68800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4212,106 +4317,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E48" s="3">
         <v>21300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>19600</v>
       </c>
       <c r="L48" s="3">
         <v>19600</v>
       </c>
       <c r="M48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="N48" s="3">
         <v>19700</v>
       </c>
       <c r="O48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="P48" s="3">
         <v>19900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>29400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>28700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>16500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4319,97 +4430,100 @@
         <v>84100</v>
       </c>
       <c r="E49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="F49" s="3">
         <v>84200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>83700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>84100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>83800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>82500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>84600</v>
       </c>
       <c r="L49" s="3">
         <v>84600</v>
       </c>
       <c r="M49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="N49" s="3">
         <v>85100</v>
       </c>
       <c r="O49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="P49" s="3">
         <v>85400</v>
       </c>
       <c r="Q49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="R49" s="3">
         <v>85300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>84300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>83900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>83800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>84600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>83800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>84200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>84600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>84600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>85700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>85100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>85000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>85300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>72600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>72400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,13 +4721,16 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
@@ -4631,79 +4751,82 @@
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>500</v>
       </c>
       <c r="M52" s="3">
+        <v>500</v>
+      </c>
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4923,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E54" s="3">
         <v>179300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>181400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>180800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>182900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>177700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>185000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>224700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>208400</v>
       </c>
       <c r="L54" s="3">
         <v>208400</v>
       </c>
       <c r="M54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="N54" s="3">
         <v>207500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>211400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>208800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>199400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>192500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>196100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>192500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>195100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>193700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>193900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>191400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>187700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>180800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>187100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>185900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>191000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>185200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>182200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>174900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>160800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>159300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,106 +5100,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>8000</v>
       </c>
       <c r="L57" s="3">
         <v>8000</v>
       </c>
       <c r="M57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N57" s="3">
         <v>7700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5166,228 +5300,237 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E59" s="3">
         <v>38100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>50900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>47300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>39900</v>
       </c>
       <c r="L59" s="3">
         <v>39900</v>
       </c>
       <c r="M59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="N59" s="3">
         <v>47200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>49900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>50900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>36500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>37500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>30500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>35200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>34200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>35500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>30200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>36800</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>34100</v>
       </c>
       <c r="AA59" s="3">
         <v>34100</v>
       </c>
       <c r="AB59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AC59" s="3">
         <v>39800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>43000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>36000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>37100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>34200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>46700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E60" s="3">
         <v>44300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>46900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>59600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51900</v>
-      </c>
-      <c r="K60" s="3">
-        <v>48000</v>
       </c>
       <c r="L60" s="3">
         <v>48000</v>
       </c>
       <c r="M60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="N60" s="3">
         <v>54900</v>
       </c>
       <c r="O60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="P60" s="3">
         <v>55600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>46200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>42600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>45100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>42300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>42300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>36600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>44200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>39200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>42500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>48400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>51400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>44600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>45200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>45800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>55800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E61" s="3">
         <v>30700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>43700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>57700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>59700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -5422,144 +5565,150 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>2500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>19000</v>
       </c>
       <c r="AC61" s="3">
         <v>19000</v>
       </c>
       <c r="AD61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>22000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E62" s="3">
         <v>10800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>10200</v>
       </c>
       <c r="L62" s="3">
         <v>10200</v>
       </c>
       <c r="M62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N62" s="3">
         <v>8800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6007,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E66" s="3">
         <v>85800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>110000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>114200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>126700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>60600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>58100</v>
       </c>
       <c r="L66" s="3">
         <v>58100</v>
       </c>
       <c r="M66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="N66" s="3">
         <v>63700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>62900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>64400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>54300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>56100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>60200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>58700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>64300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>75700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>78000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>84100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>83100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>64700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>73000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6549,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E72" s="3">
         <v>66500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>60800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>49500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>43800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>38600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>31900</v>
-      </c>
-      <c r="K72" s="3">
-        <v>18300</v>
       </c>
       <c r="L72" s="3">
         <v>18300</v>
       </c>
       <c r="M72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="N72" s="3">
         <v>11300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-15200</v>
       </c>
       <c r="S72" s="3">
         <v>-15200</v>
       </c>
       <c r="T72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="U72" s="3">
         <v>-8200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-13700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-10200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-17100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-18300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-25400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-19900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6953,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102200</v>
+      </c>
+      <c r="E76" s="3">
         <v>93500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>90100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>80800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>63400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>58300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>164100</v>
-      </c>
-      <c r="K76" s="3">
-        <v>150300</v>
       </c>
       <c r="L76" s="3">
         <v>150300</v>
       </c>
       <c r="M76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="N76" s="3">
         <v>143900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>148500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>144400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>143200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>140900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>138600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>136600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>140800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>137600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>138700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>131200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>129700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>123600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>128400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>121600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>115400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>107300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>98100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>91800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>96000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>86300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,111 +7155,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E80" s="2">
         <v>45380</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45289</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45198</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44925</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44743</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44652</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44470</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44379</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44288</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44197</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44099</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44008</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43917</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43826</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43735</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43644</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43553</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43462</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43371</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43280</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43189</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43098</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43007</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42734</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7078,97 +7273,100 @@
         <v>8700</v>
       </c>
       <c r="E81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F81" s="3">
         <v>7900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>11500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,8 +7401,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7218,7 +7417,7 @@
         <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -7230,16 +7429,16 @@
         <v>800</v>
       </c>
       <c r="K83" s="3">
+        <v>800</v>
+      </c>
+      <c r="L83" s="3">
         <v>1800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1100</v>
       </c>
       <c r="O83" s="3">
         <v>1100</v>
@@ -7248,19 +7447,19 @@
         <v>1100</v>
       </c>
       <c r="Q83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="R83" s="3">
         <v>1200</v>
       </c>
       <c r="S83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T83" s="3">
         <v>1100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1100</v>
       </c>
       <c r="V83" s="3">
         <v>1100</v>
@@ -7269,10 +7468,10 @@
         <v>1100</v>
       </c>
       <c r="X83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>900</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>1200</v>
       </c>
       <c r="Z83" s="3">
         <v>1200</v>
@@ -7287,22 +7486,25 @@
         <v>1200</v>
       </c>
       <c r="AD83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AE83" s="3">
         <v>1100</v>
       </c>
       <c r="AF83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>900</v>
       </c>
       <c r="AH83" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E89" s="3">
         <v>2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>13800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>15800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>17200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>12100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8145,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7937,7 +8158,7 @@
         <v>-900</v>
       </c>
       <c r="F91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="G91" s="3">
         <v>-1100</v>
@@ -7946,13 +8167,13 @@
         <v>-1100</v>
       </c>
       <c r="I91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1000</v>
       </c>
       <c r="L91" s="3">
         <v>-1000</v>
@@ -7961,70 +8182,73 @@
         <v>-1000</v>
       </c>
       <c r="N91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,8 +8446,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8231,7 +8461,7 @@
         <v>-900</v>
       </c>
       <c r="F94" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="G94" s="3">
         <v>-1100</v>
@@ -8240,85 +8470,88 @@
         <v>-1100</v>
       </c>
       <c r="I94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-1000</v>
       </c>
       <c r="M94" s="3">
         <v>-1000</v>
       </c>
       <c r="N94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8374,7 +8608,7 @@
         <v>-3000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3500</v>
+        <v>-3000</v>
       </c>
       <c r="J96" s="3">
         <v>-3500</v>
@@ -8383,76 +8617,79 @@
         <v>-3500</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-6400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-6100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-5800</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-5800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,106 +8988,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-60100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-26000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8897,35 +9146,35 @@
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -8941,102 +9190,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-36800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>5400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,455 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E7" s="2">
         <v>45471</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45380</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45289</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45198</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44925</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44743</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44652</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44470</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44379</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44288</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44197</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44099</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44008</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43917</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43826</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43644</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43553</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43462</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43371</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43280</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43189</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43098</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43007</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42734</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>77700</v>
+        <v>77900</v>
       </c>
       <c r="E8" s="3">
-        <v>77200</v>
+        <v>75900</v>
       </c>
       <c r="F8" s="3">
-        <v>72400</v>
+        <v>75700</v>
       </c>
       <c r="G8" s="3">
+        <v>71200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>74600</v>
+      </c>
+      <c r="I8" s="3">
+        <v>75600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>69800</v>
+      </c>
+      <c r="K8" s="3">
+        <v>70100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>72000</v>
+      </c>
+      <c r="M8" s="3">
         <v>75900</v>
       </c>
-      <c r="H8" s="3">
-        <v>77100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>71200</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
+        <v>75700</v>
+      </c>
+      <c r="O8" s="3">
+        <v>70200</v>
+      </c>
+      <c r="P8" s="3">
+        <v>71900</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>73200</v>
+      </c>
+      <c r="R8" s="3">
+        <v>63500</v>
+      </c>
+      <c r="S8" s="3">
+        <v>59300</v>
+      </c>
+      <c r="T8" s="3">
+        <v>57900</v>
+      </c>
+      <c r="U8" s="3">
+        <v>52800</v>
+      </c>
+      <c r="V8" s="3">
+        <v>69500</v>
+      </c>
+      <c r="W8" s="3">
+        <v>69100</v>
+      </c>
+      <c r="X8" s="3">
+        <v>72700</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>73500</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>67200</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>63700</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>73700</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>74500</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>71100</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>60100</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>71500</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>73600</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>71400</v>
+      </c>
+      <c r="AI8" s="3">
         <v>70100</v>
       </c>
-      <c r="K8" s="3">
-        <v>72000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>75900</v>
-      </c>
-      <c r="M8" s="3">
-        <v>75700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>70200</v>
-      </c>
-      <c r="O8" s="3">
-        <v>71900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>73200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>63500</v>
-      </c>
-      <c r="R8" s="3">
-        <v>59300</v>
-      </c>
-      <c r="S8" s="3">
-        <v>57900</v>
-      </c>
-      <c r="T8" s="3">
-        <v>52800</v>
-      </c>
-      <c r="U8" s="3">
-        <v>69500</v>
-      </c>
-      <c r="V8" s="3">
-        <v>69100</v>
-      </c>
-      <c r="W8" s="3">
-        <v>72700</v>
-      </c>
-      <c r="X8" s="3">
-        <v>73500</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>67200</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>63700</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>73700</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>74500</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>71100</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>60100</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>71500</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>73600</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>71400</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>70100</v>
-      </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>47200</v>
+        <v>46400</v>
       </c>
       <c r="E9" s="3">
-        <v>47200</v>
+        <v>45400</v>
       </c>
       <c r="F9" s="3">
+        <v>45800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>41900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>44400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>45400</v>
+      </c>
+      <c r="J9" s="3">
         <v>43100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="K9" s="3">
+        <v>40500</v>
+      </c>
+      <c r="L9" s="3">
+        <v>43900</v>
+      </c>
+      <c r="M9" s="3">
+        <v>45900</v>
+      </c>
+      <c r="N9" s="3">
+        <v>47900</v>
+      </c>
+      <c r="O9" s="3">
+        <v>42700</v>
+      </c>
+      <c r="P9" s="3">
+        <v>45700</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>43400</v>
+      </c>
+      <c r="R9" s="3">
+        <v>41200</v>
+      </c>
+      <c r="S9" s="3">
+        <v>38900</v>
+      </c>
+      <c r="T9" s="3">
+        <v>39700</v>
+      </c>
+      <c r="U9" s="3">
+        <v>40700</v>
+      </c>
+      <c r="V9" s="3">
+        <v>47100</v>
+      </c>
+      <c r="W9" s="3">
+        <v>45400</v>
+      </c>
+      <c r="X9" s="3">
+        <v>48300</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>47500</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>44600</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>40100</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>49600</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>49200</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>48300</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>38600</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>47800</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>49200</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>48300</v>
+      </c>
+      <c r="AI9" s="3">
         <v>45600</v>
       </c>
-      <c r="H9" s="3">
-        <v>46900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>44500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>40500</v>
-      </c>
-      <c r="K9" s="3">
-        <v>43900</v>
-      </c>
-      <c r="L9" s="3">
-        <v>45900</v>
-      </c>
-      <c r="M9" s="3">
-        <v>47900</v>
-      </c>
-      <c r="N9" s="3">
-        <v>42700</v>
-      </c>
-      <c r="O9" s="3">
-        <v>45700</v>
-      </c>
-      <c r="P9" s="3">
-        <v>43400</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>41200</v>
-      </c>
-      <c r="R9" s="3">
-        <v>38900</v>
-      </c>
-      <c r="S9" s="3">
-        <v>39700</v>
-      </c>
-      <c r="T9" s="3">
-        <v>40700</v>
-      </c>
-      <c r="U9" s="3">
-        <v>47100</v>
-      </c>
-      <c r="V9" s="3">
-        <v>45400</v>
-      </c>
-      <c r="W9" s="3">
-        <v>48300</v>
-      </c>
-      <c r="X9" s="3">
-        <v>47500</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>44600</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>40100</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>49600</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>49200</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>48300</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>38600</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>47800</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>49200</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>48300</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>45600</v>
-      </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E10" s="3">
         <v>30500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>30300</v>
       </c>
       <c r="H10" s="3">
         <v>30200</v>
       </c>
       <c r="I10" s="3">
+        <v>30200</v>
+      </c>
+      <c r="J10" s="3">
         <v>26700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>24400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>26000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>22600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>24100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>25300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>22800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>21500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>23700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>24400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>23100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>24500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1153,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +1255,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,22 +1359,25 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>1200</v>
-      </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1365,23 +1385,23 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1389,85 +1409,88 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>5500</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>5000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>4400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>100</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1484,8 +1507,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>8</v>
@@ -1502,12 +1525,12 @@
       <c r="U15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W15" s="3">
         <v>200</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1520,8 +1543,8 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1544,8 +1567,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,8 +1604,9 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1587,201 +1614,207 @@
         <v>65100</v>
       </c>
       <c r="E17" s="3">
-        <v>65700</v>
+        <v>63400</v>
       </c>
       <c r="F17" s="3">
+        <v>64100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>53200</v>
+      </c>
+      <c r="H17" s="3">
         <v>60900</v>
       </c>
-      <c r="G17" s="3">
-        <v>62100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>64300</v>
-      </c>
       <c r="I17" s="3">
-        <v>60000</v>
+        <v>62900</v>
       </c>
       <c r="J17" s="3">
+        <v>58600</v>
+      </c>
+      <c r="K17" s="3">
         <v>56500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>61700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>62300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>58200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>60500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>59000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>57800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>53400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>57800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>61800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>65500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>58600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>60100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>65500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>60300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>62800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>53700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>63600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>67100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>63500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>60400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12600</v>
+        <v>12800</v>
       </c>
       <c r="E18" s="3">
-        <v>11500</v>
+        <v>12500</v>
       </c>
       <c r="F18" s="3">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="G18" s="3">
-        <v>13800</v>
+        <v>18000</v>
       </c>
       <c r="H18" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I18" s="3">
         <v>12800</v>
       </c>
-      <c r="I18" s="3">
-        <v>11200</v>
-      </c>
       <c r="J18" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K18" s="3">
         <v>13600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>7900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,31 +1850,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1918,136 +1952,142 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E21" s="3">
         <v>13500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>18900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>14600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>13600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>14400</v>
+      </c>
+      <c r="L21" s="3">
+        <v>14900</v>
+      </c>
+      <c r="M21" s="3">
+        <v>16000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>14400</v>
+      </c>
+      <c r="O21" s="3">
+        <v>13000</v>
+      </c>
+      <c r="P21" s="3">
         <v>12500</v>
       </c>
-      <c r="F21" s="3">
-        <v>12400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>14600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>13600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>12100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>14400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>14900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>16000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>14400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>13000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>12500</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>10600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E22" s="3">
         <v>500</v>
       </c>
       <c r="F22" s="3">
+        <v>500</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>900</v>
       </c>
       <c r="I22" s="3">
         <v>900</v>
       </c>
       <c r="J22" s="3">
+        <v>900</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2082,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3">
         <v>100</v>
@@ -2094,7 +2134,7 @@
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>200</v>
@@ -2109,7 +2149,7 @@
         <v>200</v>
       </c>
       <c r="AF22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG22" s="3">
         <v>100</v>
@@ -2120,210 +2160,219 @@
       <c r="AI22" s="3">
         <v>100</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E23" s="3">
         <v>12000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>9600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E24" s="3">
         <v>3300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>2400</v>
       </c>
       <c r="AB24" s="3">
         <v>2400</v>
       </c>
       <c r="AC24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD24" s="3">
         <v>800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1600</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>3300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E26" s="3">
         <v>8700</v>
       </c>
       <c r="F26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G26" s="3">
         <v>7900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6900</v>
-      </c>
-      <c r="X26" s="3">
-        <v>7000</v>
       </c>
       <c r="Y26" s="3">
         <v>7000</v>
       </c>
       <c r="Z26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AA26" s="3">
         <v>3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E27" s="3">
         <v>8700</v>
       </c>
       <c r="F27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G27" s="3">
         <v>7900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6900</v>
-      </c>
-      <c r="X27" s="3">
-        <v>7000</v>
       </c>
       <c r="Y27" s="3">
         <v>7000</v>
       </c>
       <c r="Z27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AA27" s="3">
         <v>3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>11700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2777,11 +2838,11 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-200</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2792,29 +2853,29 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-100</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>5800</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2827,8 +2888,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,31 +3096,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3130,109 +3200,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E33" s="3">
         <v>8700</v>
       </c>
       <c r="F33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G33" s="3">
         <v>7900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>11500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>6200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E35" s="3">
         <v>8700</v>
       </c>
       <c r="F35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G35" s="3">
         <v>7900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>11500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>6200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E38" s="2">
         <v>45471</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45380</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45289</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45198</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44925</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44743</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44652</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44470</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44379</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44288</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44197</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44099</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44008</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43917</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43826</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43644</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43553</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43462</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43371</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43280</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43189</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43098</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43007</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42734</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,109 +3699,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>67000</v>
-      </c>
-      <c r="L41" s="3">
-        <v>47800</v>
       </c>
       <c r="M41" s="3">
         <v>47800</v>
       </c>
       <c r="N41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="O41" s="3">
         <v>45800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>49500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>23300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>23700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>17500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>16200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>17100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>19700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,132 +3905,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E43" s="3">
         <v>58100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>58000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>52100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>62200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>57800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>52000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>48400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>50500</v>
       </c>
       <c r="M43" s="3">
         <v>50500</v>
       </c>
       <c r="N43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="O43" s="3">
         <v>50600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>49600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>47200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>38500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>32800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>36200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>37000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>53400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>49800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>57900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>54500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>56000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>54800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>56900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>56800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>51900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>52300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>55600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>50400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>49900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>47400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4017,233 +4113,242 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L45" s="3">
         <v>3200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>5400</v>
       </c>
       <c r="M45" s="3">
         <v>5400</v>
       </c>
       <c r="N45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="O45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E46" s="3">
         <v>80300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>76800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>72000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>81200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>122400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>103600</v>
       </c>
       <c r="M46" s="3">
         <v>103600</v>
       </c>
       <c r="N46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="O46" s="3">
         <v>102200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>105700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>102300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>92400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>84800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>82700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>78100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>80000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>78600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>78000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>75300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>70700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>73100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>73800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>73300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>79100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>75300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>74700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>68000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>69600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>68800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4320,210 +4425,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E48" s="3">
         <v>22800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>19600</v>
       </c>
       <c r="M48" s="3">
         <v>19600</v>
       </c>
       <c r="N48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="O48" s="3">
         <v>19700</v>
       </c>
       <c r="P48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="Q48" s="3">
         <v>19900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>28500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>29400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>28900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>24300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>16500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>84100</v>
+        <v>92200</v>
       </c>
       <c r="E49" s="3">
         <v>84100</v>
       </c>
       <c r="F49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="G49" s="3">
         <v>84200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>83700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>84100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>83500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>82500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>84600</v>
       </c>
       <c r="M49" s="3">
         <v>84600</v>
       </c>
       <c r="N49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="O49" s="3">
         <v>85100</v>
       </c>
       <c r="P49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="Q49" s="3">
         <v>85400</v>
       </c>
       <c r="R49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="S49" s="3">
         <v>85300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>83900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>83800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>84600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>83800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>84200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>84200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>85700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>85100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>85000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>85300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>72600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>72400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,8 +4841,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4733,7 +4853,7 @@
         <v>400</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -4754,79 +4874,82 @@
         <v>300</v>
       </c>
       <c r="L52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="M52" s="3">
         <v>500</v>
       </c>
       <c r="N52" s="3">
+        <v>500</v>
+      </c>
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5049,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>190800</v>
+      </c>
+      <c r="E54" s="3">
         <v>187500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>179300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>181400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>180800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>182900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>177700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>185000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>224700</v>
-      </c>
-      <c r="L54" s="3">
-        <v>208400</v>
       </c>
       <c r="M54" s="3">
         <v>208400</v>
       </c>
       <c r="N54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="O54" s="3">
         <v>207500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>211400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>208800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>199400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>192500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>196100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>192500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>195100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>193700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>193900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>191400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>187700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>180800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>187100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>185900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>191000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>185200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>182200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>174900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>160800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>159300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,132 +5231,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>8000</v>
       </c>
       <c r="M57" s="3">
         <v>8000</v>
       </c>
       <c r="N57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O57" s="3">
         <v>7700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5303,237 +5437,246 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>42500</v>
+        <v>19900</v>
       </c>
       <c r="E59" s="3">
-        <v>38100</v>
+        <v>20600</v>
       </c>
       <c r="F59" s="3">
-        <v>42300</v>
+        <v>20400</v>
       </c>
       <c r="G59" s="3">
-        <v>41900</v>
+        <v>17400</v>
       </c>
       <c r="H59" s="3">
-        <v>41400</v>
+        <v>19900</v>
       </c>
       <c r="I59" s="3">
-        <v>39400</v>
+        <v>21000</v>
       </c>
       <c r="J59" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K59" s="3">
         <v>50900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47300</v>
-      </c>
-      <c r="L59" s="3">
-        <v>39900</v>
       </c>
       <c r="M59" s="3">
         <v>39900</v>
       </c>
       <c r="N59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="O59" s="3">
         <v>47200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>50900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>41200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>36500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>40100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>37500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>30500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>35200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>34200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>35500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>30200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>36800</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>34100</v>
       </c>
       <c r="AB59" s="3">
         <v>34100</v>
       </c>
       <c r="AC59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AD59" s="3">
         <v>39800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>43000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>36000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>37100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>34200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>46700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E60" s="3">
         <v>46800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>59600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51900</v>
-      </c>
-      <c r="L60" s="3">
-        <v>48000</v>
       </c>
       <c r="M60" s="3">
         <v>48000</v>
       </c>
       <c r="N60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="O60" s="3">
         <v>54900</v>
       </c>
       <c r="P60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="Q60" s="3">
         <v>55600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>46200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>42600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>45100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>42300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>42300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>36600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>44200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>39200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>42500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>48400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>51400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>44600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>45200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>45800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>55800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>26700</v>
+        <v>21800</v>
       </c>
       <c r="E61" s="3">
-        <v>30700</v>
+        <v>28900</v>
       </c>
       <c r="F61" s="3">
-        <v>32700</v>
+        <v>31400</v>
       </c>
       <c r="G61" s="3">
-        <v>43700</v>
+        <v>33300</v>
       </c>
       <c r="H61" s="3">
-        <v>52700</v>
+        <v>44500</v>
       </c>
       <c r="I61" s="3">
-        <v>57700</v>
+        <v>53800</v>
       </c>
       <c r="J61" s="3">
+        <v>59100</v>
+      </c>
+      <c r="K61" s="3">
         <v>59700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5568,147 +5711,153 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>2500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>19000</v>
       </c>
       <c r="AD61" s="3">
         <v>19000</v>
       </c>
       <c r="AE61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>22000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>11700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>10800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>8700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>9300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>10500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>10300</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>7500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>10200</v>
       </c>
       <c r="M62" s="3">
         <v>10200</v>
       </c>
       <c r="N62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O62" s="3">
         <v>8800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>17800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>10200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6165,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E66" s="3">
         <v>85300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>85800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>114200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>126700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>60600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>58100</v>
       </c>
       <c r="M66" s="3">
         <v>58100</v>
       </c>
       <c r="N66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="O66" s="3">
         <v>63700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>62900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>64400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>57500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>54300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>56100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>55200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>60200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>57200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>58700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>64300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>75700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>78000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>84100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>83100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>64700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>73000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E72" s="3">
         <v>72200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>66500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>60800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>56000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>49500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>43800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>38600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31900</v>
-      </c>
-      <c r="L72" s="3">
-        <v>18300</v>
       </c>
       <c r="M72" s="3">
         <v>18300</v>
       </c>
       <c r="N72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="O72" s="3">
         <v>11300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-15200</v>
       </c>
       <c r="T72" s="3">
         <v>-15200</v>
       </c>
       <c r="U72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="V72" s="3">
         <v>-8200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-13700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-10200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-17100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-25400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E76" s="3">
         <v>102200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>93500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>90100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>80800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>63400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>164100</v>
-      </c>
-      <c r="L76" s="3">
-        <v>150300</v>
       </c>
       <c r="M76" s="3">
         <v>150300</v>
       </c>
       <c r="N76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="O76" s="3">
         <v>143900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>148500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>144400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>143200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>140900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>138600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>136600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>140800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>137600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>138700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>131200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>129700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>123600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>128400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>121600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>115400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>107300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>98100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>91800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>96000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>86300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E80" s="2">
         <v>45471</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45380</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45289</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45198</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44925</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44743</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44652</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44470</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44379</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44288</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44197</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44099</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44008</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43917</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43826</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43644</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43553</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43462</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43371</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43280</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43189</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43098</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43007</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42734</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E81" s="3">
         <v>8700</v>
       </c>
       <c r="F81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G81" s="3">
         <v>7900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>11500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>6200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,8 +7600,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7411,13 +7610,13 @@
         <v>900</v>
       </c>
       <c r="E83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -7432,16 +7631,16 @@
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1100</v>
       </c>
       <c r="P83" s="3">
         <v>1100</v>
@@ -7450,19 +7649,19 @@
         <v>1100</v>
       </c>
       <c r="R83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="S83" s="3">
         <v>1200</v>
       </c>
       <c r="T83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U83" s="3">
         <v>1100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1000</v>
-      </c>
-      <c r="V83" s="3">
-        <v>1100</v>
       </c>
       <c r="W83" s="3">
         <v>1100</v>
@@ -7471,10 +7670,10 @@
         <v>1100</v>
       </c>
       <c r="Y83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z83" s="3">
         <v>900</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>1200</v>
       </c>
       <c r="AA83" s="3">
         <v>1200</v>
@@ -7489,22 +7688,25 @@
         <v>1200</v>
       </c>
       <c r="AE83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AF83" s="3">
         <v>1100</v>
       </c>
       <c r="AG83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>900</v>
       </c>
       <c r="AI83" s="3">
         <v>900</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>900</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8222,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E89" s="3">
         <v>13700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>24300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>13800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>10100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>15800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>17200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>12100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,13 +8366,14 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="E91" s="3">
         <v>-900</v>
@@ -8161,7 +8382,7 @@
         <v>-900</v>
       </c>
       <c r="G91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="H91" s="3">
         <v>-1100</v>
@@ -8170,13 +8391,13 @@
         <v>-1100</v>
       </c>
       <c r="J91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1000</v>
       </c>
       <c r="M91" s="3">
         <v>-1000</v>
@@ -8185,70 +8406,73 @@
         <v>-1000</v>
       </c>
       <c r="O91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,13 +8676,16 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-900</v>
+        <v>-7800</v>
       </c>
       <c r="E94" s="3">
         <v>-900</v>
@@ -8464,7 +8694,7 @@
         <v>-900</v>
       </c>
       <c r="G94" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="H94" s="3">
         <v>-1100</v>
@@ -8473,85 +8703,88 @@
         <v>-1100</v>
       </c>
       <c r="J94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-1000</v>
       </c>
       <c r="N94" s="3">
         <v>-1000</v>
       </c>
       <c r="O94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,31 +8820,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="G96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="H96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="J96" s="3">
-        <v>-3500</v>
+        <v>3000</v>
       </c>
       <c r="K96" s="3">
         <v>-3500</v>
@@ -8620,76 +8854,79 @@
         <v>-3500</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-6400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-6100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-5800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,109 +9234,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-60100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-26000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9149,35 +9398,35 @@
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
@@ -9193,105 +9442,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E102" s="3">
         <v>6200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-36800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>5400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,468 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45653</v>
+      </c>
+      <c r="E7" s="2">
         <v>45562</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45471</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45380</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45289</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45198</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44925</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44743</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44652</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44470</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44379</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44288</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44197</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44099</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44008</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43917</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43826</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43644</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43553</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43462</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43371</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43280</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43189</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43098</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43007</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42734</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E8" s="3">
         <v>77900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>75900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>74600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>69800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>70100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>72000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>75900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>70200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>71900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>73200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>63500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>59300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>57900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>52800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>69500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>69100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>72700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>73500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>67200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>63700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>73700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>74500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>71100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>60100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>71500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>73600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>71400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>70100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E9" s="3">
         <v>46400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>41900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>44400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>40500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>45700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>43400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>41200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>38900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>39700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>40700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>47100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>45400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>48300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>47500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>44600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>40100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>49600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>49200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>48300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>38600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>47800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>49200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>48300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>45600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E10" s="3">
         <v>31500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>29300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>30200</v>
       </c>
       <c r="I10" s="3">
         <v>30200</v>
       </c>
       <c r="J10" s="3">
+        <v>30200</v>
+      </c>
+      <c r="K10" s="3">
         <v>26700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>26200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>20400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>12100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>24400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>26000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>22800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>23700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>24400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>23100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,25 +1378,28 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>1200</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1388,23 +1407,23 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1412,67 +1431,70 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>5500</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>5000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>4400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>100</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
         <v>900</v>
@@ -1487,13 +1509,13 @@
         <v>900</v>
       </c>
       <c r="I15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J15" s="3">
         <v>800</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1510,8 +1532,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
@@ -1528,12 +1550,12 @@
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X15" s="3">
         <v>200</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1546,8 +1568,8 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1570,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E17" s="3">
         <v>65100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>63400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>64100</v>
       </c>
-      <c r="G17" s="3">
-        <v>53200</v>
-      </c>
       <c r="H17" s="3">
+        <v>58500</v>
+      </c>
+      <c r="I17" s="3">
         <v>60900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>62900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>56500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>58000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>61700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>62300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>58200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>60500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>59000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>54600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>57800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>61800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>65500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>63800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>58600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>60100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>65500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>60300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>62800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>53700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>63600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>67100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>63500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>60400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>12800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11600</v>
       </c>
-      <c r="G18" s="3">
-        <v>18000</v>
-      </c>
       <c r="H18" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I18" s="3">
         <v>13700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,8 +1883,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1877,8 +1910,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1955,142 +1988,148 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E21" s="3">
         <v>13700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12600</v>
       </c>
-      <c r="G21" s="3">
-        <v>18900</v>
-      </c>
       <c r="H21" s="3">
+        <v>13500</v>
+      </c>
+      <c r="I21" s="3">
         <v>14600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>10800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>15500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>10600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>500</v>
       </c>
       <c r="F22" s="3">
         <v>500</v>
       </c>
       <c r="G22" s="3">
+        <v>500</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>900</v>
       </c>
       <c r="J22" s="3">
         <v>900</v>
       </c>
       <c r="K22" s="3">
+        <v>900</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -2125,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
@@ -2137,7 +2176,7 @@
         <v>100</v>
       </c>
       <c r="AB22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
@@ -2152,7 +2191,7 @@
         <v>200</v>
       </c>
       <c r="AG22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH22" s="3">
         <v>100</v>
@@ -2163,216 +2202,225 @@
       <c r="AJ22" s="3">
         <v>100</v>
       </c>
+      <c r="AK22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E23" s="3">
         <v>12400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>14100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>3800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>2400</v>
       </c>
       <c r="AC24" s="3">
         <v>2400</v>
       </c>
       <c r="AD24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AE24" s="3">
         <v>800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1600</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E26" s="3">
         <v>8600</v>
-      </c>
-      <c r="E26" s="3">
-        <v>8700</v>
       </c>
       <c r="F26" s="3">
         <v>8700</v>
       </c>
       <c r="G26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H26" s="3">
         <v>7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6900</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>7000</v>
       </c>
       <c r="Z26" s="3">
         <v>7000</v>
       </c>
       <c r="AA26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB26" s="3">
         <v>3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>11700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>7900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3">
         <v>8600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>8700</v>
       </c>
       <c r="F27" s="3">
         <v>8700</v>
       </c>
       <c r="G27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H27" s="3">
         <v>7900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6900</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>7000</v>
       </c>
       <c r="Z27" s="3">
         <v>7000</v>
       </c>
       <c r="AA27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB27" s="3">
         <v>3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>11700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2841,11 +2901,11 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-200</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2856,29 +2916,29 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>5800</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2891,8 +2951,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,8 +3165,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3125,8 +3194,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3203,112 +3272,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E33" s="3">
         <v>8600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>8700</v>
       </c>
       <c r="F33" s="3">
         <v>8700</v>
       </c>
       <c r="G33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H33" s="3">
         <v>7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>11500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E35" s="3">
         <v>8600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>8700</v>
       </c>
       <c r="F35" s="3">
         <v>8700</v>
       </c>
       <c r="G35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H35" s="3">
         <v>7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>11500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45653</v>
+      </c>
+      <c r="E38" s="2">
         <v>45562</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45471</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45380</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45289</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45198</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44925</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44743</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44652</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44470</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44379</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44288</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44197</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44099</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44008</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43917</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43826</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43644</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43553</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43462</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43371</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43280</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43189</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43098</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43007</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42734</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,112 +3785,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E41" s="3">
         <v>10000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>67000</v>
-      </c>
-      <c r="M41" s="3">
-        <v>47800</v>
       </c>
       <c r="N41" s="3">
         <v>47800</v>
       </c>
       <c r="O41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="P41" s="3">
         <v>45800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>51100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>49500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>23300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>23700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>17500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>17100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>19700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3908,112 +3997,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E43" s="3">
         <v>61200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>58100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>58000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>52100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>62200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>52100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>50500</v>
       </c>
       <c r="N43" s="3">
         <v>50500</v>
       </c>
       <c r="O43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="P43" s="3">
         <v>50600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>49600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>47200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>38500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>32800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>36200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>37000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>53400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>49800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>57900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>54500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>56000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>54800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>56900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>56800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>51900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>52300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>55600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>50400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>49900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4038,8 +4133,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4116,8 +4211,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4142,190 +4240,196 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>2500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>5400</v>
       </c>
       <c r="N45" s="3">
         <v>5400</v>
       </c>
       <c r="O45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E46" s="3">
         <v>74900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>80300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>73700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>76800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>72000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>81200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>122400</v>
-      </c>
-      <c r="M46" s="3">
-        <v>103600</v>
       </c>
       <c r="N46" s="3">
         <v>103600</v>
       </c>
       <c r="O46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="P46" s="3">
         <v>102200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>105700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>102300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>92400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>84800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>82700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>78100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>80000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>78600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>78000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>75300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>70700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>73100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>73800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>73300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>79100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>75300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>74700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>68000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>69600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4350,8 +4454,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4428,216 +4532,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E48" s="3">
         <v>23300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>19600</v>
       </c>
       <c r="N48" s="3">
         <v>19600</v>
       </c>
       <c r="O48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="P48" s="3">
         <v>19700</v>
       </c>
       <c r="Q48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="R48" s="3">
         <v>19900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>28500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>29100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>29400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>28700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>28900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>24300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>16500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>14800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E49" s="3">
         <v>92200</v>
-      </c>
-      <c r="E49" s="3">
-        <v>84100</v>
       </c>
       <c r="F49" s="3">
         <v>84100</v>
       </c>
       <c r="G49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="H49" s="3">
         <v>84200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>83700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>84100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>83800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>83500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>82500</v>
-      </c>
-      <c r="M49" s="3">
-        <v>84600</v>
       </c>
       <c r="N49" s="3">
         <v>84600</v>
       </c>
       <c r="O49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="P49" s="3">
         <v>85100</v>
       </c>
       <c r="Q49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="R49" s="3">
         <v>85400</v>
       </c>
       <c r="S49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="T49" s="3">
         <v>85300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>84300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>83900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>83800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>84600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>83800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>84600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>84700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>85700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>85100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>85000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>85300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>72600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>72400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,8 +4960,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4856,7 +4975,7 @@
         <v>400</v>
       </c>
       <c r="F52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
@@ -4877,79 +4996,82 @@
         <v>300</v>
       </c>
       <c r="M52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N52" s="3">
         <v>500</v>
       </c>
       <c r="O52" s="3">
+        <v>500</v>
+      </c>
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>191900</v>
+      </c>
+      <c r="E54" s="3">
         <v>190800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>187500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>179300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>181400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>180800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>182900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>177700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>185000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>224700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>208400</v>
       </c>
       <c r="N54" s="3">
         <v>208400</v>
       </c>
       <c r="O54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="P54" s="3">
         <v>207500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>211400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>208800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>199400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>192500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>196100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>192500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>195100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>193700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>193900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>191400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>187700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>180800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>187100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>185900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>191000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>185200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>182200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>174900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>160800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>159300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,138 +5361,142 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E57" s="3">
         <v>5300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>8000</v>
       </c>
       <c r="N57" s="3">
         <v>8000</v>
       </c>
       <c r="O57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="P57" s="3">
         <v>7700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1200</v>
       </c>
       <c r="J58" s="3">
         <v>1200</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5440,246 +5573,255 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E59" s="3">
         <v>19900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>50900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47300</v>
-      </c>
-      <c r="M59" s="3">
-        <v>39900</v>
       </c>
       <c r="N59" s="3">
         <v>39900</v>
       </c>
       <c r="O59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="P59" s="3">
         <v>47200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>50900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>41200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>36500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>40100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>37500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>30500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>35200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>34200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>35500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>30200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>36800</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>34100</v>
       </c>
       <c r="AC59" s="3">
         <v>34100</v>
       </c>
       <c r="AD59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AE59" s="3">
         <v>39800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>43000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>36000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>37100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>34200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>46700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E60" s="3">
         <v>49500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>46800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>49900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>46300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51900</v>
-      </c>
-      <c r="M60" s="3">
-        <v>48000</v>
       </c>
       <c r="N60" s="3">
         <v>48000</v>
       </c>
       <c r="O60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="P60" s="3">
         <v>54900</v>
       </c>
       <c r="Q60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="R60" s="3">
         <v>55600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>46200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>42600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>45100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>42300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>39400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>42300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>36600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>44200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>39200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>42500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>48400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>51400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>44600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>45200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>45800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>55800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E61" s="3">
         <v>21800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>44500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>59100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>59700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5714,46 +5856,49 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>2500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>19000</v>
       </c>
       <c r="AE61" s="3">
         <v>19000</v>
       </c>
       <c r="AF61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>22000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5778,86 +5923,89 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>7500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>10200</v>
       </c>
       <c r="N62" s="3">
         <v>10200</v>
       </c>
       <c r="O62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P62" s="3">
         <v>8800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>17500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>17800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E66" s="3">
         <v>79800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>85300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>85800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>110000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>114200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>126700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60600</v>
-      </c>
-      <c r="M66" s="3">
-        <v>58100</v>
       </c>
       <c r="N66" s="3">
         <v>58100</v>
       </c>
       <c r="O66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="P66" s="3">
         <v>63700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>62900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>64400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>57500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>54300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>55200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>60200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>57900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>58700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>64300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>75700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>78000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>84100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>83100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>64700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E72" s="3">
         <v>77800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>72200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>60800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>49500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>43800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>38600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31900</v>
-      </c>
-      <c r="M72" s="3">
-        <v>18300</v>
       </c>
       <c r="N72" s="3">
         <v>18300</v>
       </c>
       <c r="O72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="P72" s="3">
         <v>11300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-14300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-15200</v>
       </c>
       <c r="U72" s="3">
         <v>-15200</v>
       </c>
       <c r="V72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="W72" s="3">
         <v>-8200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-13700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-17100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-25400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-19900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E76" s="3">
         <v>110900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>102200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>93500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>90100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>80800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>72900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>63400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>164100</v>
-      </c>
-      <c r="M76" s="3">
-        <v>150300</v>
       </c>
       <c r="N76" s="3">
         <v>150300</v>
       </c>
       <c r="O76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="P76" s="3">
         <v>143900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>148500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>144400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>143200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>140900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>138600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>136600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>140800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>137600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>138700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>131200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>129700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>123600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>128400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>121600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>115400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>107300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>98100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>91800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>96000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>86300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45653</v>
+      </c>
+      <c r="E80" s="2">
         <v>45562</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45471</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45380</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45289</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45198</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44925</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44743</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44652</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44470</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44379</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44288</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44197</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44099</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44008</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43917</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43826</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43644</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43553</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43462</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43371</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43280</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43189</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43098</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43007</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42734</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E81" s="3">
         <v>8600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>8700</v>
       </c>
       <c r="F81" s="3">
         <v>8700</v>
       </c>
       <c r="G81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H81" s="3">
         <v>7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>11500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,8 +7798,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7610,7 +7808,7 @@
         <v>900</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
@@ -7634,16 +7832,16 @@
         <v>800</v>
       </c>
       <c r="M83" s="3">
+        <v>800</v>
+      </c>
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1100</v>
       </c>
       <c r="Q83" s="3">
         <v>1100</v>
@@ -7652,19 +7850,19 @@
         <v>1100</v>
       </c>
       <c r="S83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="T83" s="3">
         <v>1200</v>
       </c>
       <c r="U83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V83" s="3">
         <v>1100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>1100</v>
       </c>
       <c r="X83" s="3">
         <v>1100</v>
@@ -7673,10 +7871,10 @@
         <v>1100</v>
       </c>
       <c r="Z83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA83" s="3">
         <v>900</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>1200</v>
       </c>
       <c r="AB83" s="3">
         <v>1200</v>
@@ -7691,22 +7889,25 @@
         <v>1200</v>
       </c>
       <c r="AF83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AG83" s="3">
         <v>1100</v>
       </c>
       <c r="AH83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AI83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>900</v>
       </c>
       <c r="AJ83" s="3">
         <v>900</v>
       </c>
+      <c r="AK83" s="3">
+        <v>900</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E89" s="3">
         <v>10600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>24300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>9500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>17200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>10000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,16 +8586,17 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-900</v>
       </c>
       <c r="F91" s="3">
         <v>-900</v>
@@ -8385,7 +8605,7 @@
         <v>-900</v>
       </c>
       <c r="H91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="I91" s="3">
         <v>-1100</v>
@@ -8394,13 +8614,13 @@
         <v>-1100</v>
       </c>
       <c r="K91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1000</v>
       </c>
       <c r="N91" s="3">
         <v>-1000</v>
@@ -8409,70 +8629,73 @@
         <v>-1000</v>
       </c>
       <c r="P91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,16 +8905,19 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7800</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-900</v>
       </c>
       <c r="F94" s="3">
         <v>-900</v>
@@ -8697,7 +8926,7 @@
         <v>-900</v>
       </c>
       <c r="H94" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="I94" s="3">
         <v>-1100</v>
@@ -8706,85 +8935,88 @@
         <v>-1100</v>
       </c>
       <c r="K94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-1000</v>
       </c>
       <c r="O94" s="3">
         <v>-1000</v>
       </c>
       <c r="P94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8848,7 +9081,7 @@
         <v>3000</v>
       </c>
       <c r="K96" s="3">
-        <v>-3500</v>
+        <v>3000</v>
       </c>
       <c r="L96" s="3">
         <v>-3500</v>
@@ -8857,76 +9090,79 @@
         <v>-3500</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-6400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-6100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-5800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,112 +9479,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-60100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-26000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-11500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9401,35 +9649,35 @@
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -9445,108 +9693,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E7" s="2">
         <v>45653</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45562</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45471</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45380</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45289</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45198</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44925</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44743</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44652</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44470</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44379</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44288</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44197</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44099</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44008</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43917</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43826</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43644</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43553</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43462</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43371</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43280</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43189</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43098</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43007</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42734</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E8" s="3">
         <v>77500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>77900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>74600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>69800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>70100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>72000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>73200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>63500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>59300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>57900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>52800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>69500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>69100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>72700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>73500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>67200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>63700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>73700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>74500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>71100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>60100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>71500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>73600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>71400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>70100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E9" s="3">
         <v>46200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>45800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>41900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>44400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>43100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>40500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>42700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>45700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>43400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>41200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>38900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>39700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>47100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>45400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>48300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>47500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>44600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>40100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>49600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>49200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>48300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>38600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>47800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>49200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>45600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E10" s="3">
         <v>31200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>29300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>30200</v>
       </c>
       <c r="J10" s="3">
         <v>30200</v>
       </c>
       <c r="K10" s="3">
+        <v>30200</v>
+      </c>
+      <c r="L10" s="3">
         <v>26700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>26200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>29800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>20400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>12100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>24400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>26000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>25300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>22800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>23700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>24400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>24500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,52 +1398,55 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1434,70 +1454,73 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>5500</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>5000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>4400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>100</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
         <v>1100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>900</v>
       </c>
       <c r="F15" s="3">
         <v>900</v>
@@ -1512,13 +1535,13 @@
         <v>900</v>
       </c>
       <c r="J15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>800</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1535,8 +1558,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
@@ -1553,12 +1576,12 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3">
         <v>200</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1571,8 +1594,8 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E17" s="3">
         <v>69700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>65100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>63400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>64100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>58500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>60900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>62900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>56500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>58000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>61700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>58200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>60500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>59000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>54600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>57800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>57800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>61800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>65500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>63300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>58600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>60100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>65500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>60300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>62800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>53700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>63600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>67100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>63500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>60400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>7700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>7900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>9700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1917,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1913,8 +1947,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1991,115 +2025,121 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E21" s="3">
         <v>8800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>15300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>10500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>10800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>15500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2107,32 +2147,32 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>500</v>
       </c>
       <c r="G22" s="3">
         <v>500</v>
       </c>
       <c r="H22" s="3">
+        <v>500</v>
+      </c>
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>900</v>
       </c>
       <c r="K22" s="3">
         <v>900</v>
       </c>
       <c r="L22" s="3">
+        <v>900</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2167,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
@@ -2179,7 +2219,7 @@
         <v>100</v>
       </c>
       <c r="AC22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>200</v>
@@ -2194,7 +2234,7 @@
         <v>200</v>
       </c>
       <c r="AH22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI22" s="3">
         <v>100</v>
@@ -2205,222 +2245,231 @@
       <c r="AK22" s="3">
         <v>100</v>
       </c>
+      <c r="AL22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>7500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>14100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>9600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>2400</v>
       </c>
       <c r="AD24" s="3">
         <v>2400</v>
       </c>
       <c r="AE24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF24" s="3">
         <v>800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1600</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>3300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>8700</v>
       </c>
       <c r="G26" s="3">
         <v>8700</v>
       </c>
       <c r="H26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I26" s="3">
         <v>7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6900</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>7000</v>
       </c>
       <c r="AA26" s="3">
         <v>7000</v>
       </c>
       <c r="AB26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC26" s="3">
         <v>3300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>11700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>6200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>8700</v>
       </c>
       <c r="G27" s="3">
         <v>8700</v>
       </c>
       <c r="H27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I27" s="3">
         <v>7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6900</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>7000</v>
       </c>
       <c r="AA27" s="3">
         <v>7000</v>
       </c>
       <c r="AB27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC27" s="3">
         <v>3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>6200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2904,11 +2965,11 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -2919,29 +2980,29 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-500</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>5800</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3235,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3197,8 +3267,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3275,115 +3345,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>8700</v>
       </c>
       <c r="G33" s="3">
         <v>8700</v>
       </c>
       <c r="H33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I33" s="3">
         <v>7900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>6200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>8700</v>
       </c>
       <c r="G35" s="3">
         <v>8700</v>
       </c>
       <c r="H35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I35" s="3">
         <v>7900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>6200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E38" s="2">
         <v>45653</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45562</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45471</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45380</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45289</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45198</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44925</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44743</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44652</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44470</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44379</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44288</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44197</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44099</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44008</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43917</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43826</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43644</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43553</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43462</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43371</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43280</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43189</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43098</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43007</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42734</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3872,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>67000</v>
-      </c>
-      <c r="N41" s="3">
-        <v>47800</v>
       </c>
       <c r="O41" s="3">
         <v>47800</v>
       </c>
       <c r="P41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="Q41" s="3">
         <v>45800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>51100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>49500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>43200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>37400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>23300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>23700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>17500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>16200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>19700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4000,115 +4090,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E43" s="3">
         <v>57100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>61200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>58100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>52100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>62200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>57800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>52100</v>
-      </c>
-      <c r="N43" s="3">
-        <v>50500</v>
       </c>
       <c r="O43" s="3">
         <v>50500</v>
       </c>
       <c r="P43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="Q43" s="3">
         <v>50600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>49600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>47200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>38500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>32800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>36200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>37000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>53400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>49800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>57900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>54500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>56000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>54800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>56900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>56800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>51900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>52300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>55600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>50400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>49900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>47400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4136,8 +4232,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4214,8 +4310,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4243,193 +4342,199 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>2500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>5400</v>
       </c>
       <c r="O45" s="3">
         <v>5400</v>
       </c>
       <c r="P45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Q45" s="3">
         <v>5800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E46" s="3">
         <v>76300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>80300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>73700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>75300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>76800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>72000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>81200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>122400</v>
-      </c>
-      <c r="N46" s="3">
-        <v>103600</v>
       </c>
       <c r="O46" s="3">
         <v>103600</v>
       </c>
       <c r="P46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="Q46" s="3">
         <v>102200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>105700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>102300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>92400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>84800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>82700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>78100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>80000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>78600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>78000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>75300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>70700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>73100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>73800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>73300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>79100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>75300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>74700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>68000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>69600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>68800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4457,8 +4562,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4535,222 +4640,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>19600</v>
       </c>
       <c r="O48" s="3">
         <v>19600</v>
       </c>
       <c r="P48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="Q48" s="3">
         <v>19700</v>
       </c>
       <c r="R48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="S48" s="3">
         <v>19900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>28500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>29100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>29400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>28700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>28900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>24300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>22800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>16500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>15800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E49" s="3">
         <v>92100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>92200</v>
-      </c>
-      <c r="F49" s="3">
-        <v>84100</v>
       </c>
       <c r="G49" s="3">
         <v>84100</v>
       </c>
       <c r="H49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="I49" s="3">
         <v>84200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>83800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>83500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>82500</v>
-      </c>
-      <c r="N49" s="3">
-        <v>84600</v>
       </c>
       <c r="O49" s="3">
         <v>84600</v>
       </c>
       <c r="P49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="Q49" s="3">
         <v>85100</v>
       </c>
       <c r="R49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="S49" s="3">
         <v>85400</v>
       </c>
       <c r="T49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="U49" s="3">
         <v>85300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>84300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>83900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>83800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>84600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>83800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>84200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>84600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>84700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>85700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>85100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>85000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>85300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>72400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5080,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4978,7 +5098,7 @@
         <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
@@ -4999,79 +5119,82 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>500</v>
       </c>
       <c r="P52" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>191800</v>
+      </c>
+      <c r="E54" s="3">
         <v>191900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>190800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>187500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>179300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>181400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>180800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>182900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>177700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>185000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>224700</v>
-      </c>
-      <c r="N54" s="3">
-        <v>208400</v>
       </c>
       <c r="O54" s="3">
         <v>208400</v>
       </c>
       <c r="P54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="Q54" s="3">
         <v>207500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>211400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>208800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>199400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>192500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>196100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>192500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>195100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>193700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>193900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>191400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>187700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>180800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>187100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>185900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>191000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>185200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>182200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>174900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>160800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>159300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,144 +5492,148 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>8000</v>
       </c>
       <c r="O57" s="3">
         <v>8000</v>
       </c>
       <c r="P57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>7700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1200</v>
       </c>
       <c r="K58" s="3">
         <v>1200</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5576,255 +5710,264 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E59" s="3">
         <v>19700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>50900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>47300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>39900</v>
       </c>
       <c r="O59" s="3">
         <v>39900</v>
       </c>
       <c r="P59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="Q59" s="3">
         <v>47200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>50900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>41200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>36500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>40100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>37500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>30500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>35200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>34200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>35500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>30200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>36800</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>34100</v>
       </c>
       <c r="AD59" s="3">
         <v>34100</v>
       </c>
       <c r="AE59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AF59" s="3">
         <v>39800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>43000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>36000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>37100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>34200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>46700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E60" s="3">
         <v>53100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>46800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>49900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>46900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>59600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51900</v>
-      </c>
-      <c r="N60" s="3">
-        <v>48000</v>
       </c>
       <c r="O60" s="3">
         <v>48000</v>
       </c>
       <c r="P60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="Q60" s="3">
         <v>54900</v>
       </c>
       <c r="R60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="S60" s="3">
         <v>55600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>46200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>42600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>45100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>42300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>43700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>42300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>36600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>44200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>39200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>42500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>48400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>51400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>44600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>45200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>45800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>55800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E61" s="3">
         <v>14700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>44500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>59100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>59700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5859,46 +6002,49 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>2500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>19000</v>
       </c>
       <c r="AF61" s="3">
         <v>19000</v>
       </c>
       <c r="AG61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>22000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5926,86 +6072,89 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>7500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>10200</v>
       </c>
       <c r="O62" s="3">
         <v>10200</v>
       </c>
       <c r="P62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>8800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>17500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>10200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E66" s="3">
         <v>76300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>79800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>85300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>91300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>100000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>110000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>114200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>126700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>60600</v>
-      </c>
-      <c r="N66" s="3">
-        <v>58100</v>
       </c>
       <c r="O66" s="3">
         <v>58100</v>
       </c>
       <c r="P66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="Q66" s="3">
         <v>63700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>62900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>57500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>54300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>56100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>55200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>60200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>58700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>64300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>75700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>78000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>84100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>83100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>64700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>73000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E72" s="3">
         <v>78300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>77800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>72200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>66500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>60800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>49500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>43800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31900</v>
-      </c>
-      <c r="N72" s="3">
-        <v>18300</v>
       </c>
       <c r="O72" s="3">
         <v>18300</v>
       </c>
       <c r="P72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="Q72" s="3">
         <v>11300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-14300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-15200</v>
       </c>
       <c r="V72" s="3">
         <v>-15200</v>
       </c>
       <c r="W72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="X72" s="3">
         <v>-8200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-13700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-25400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-19900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E76" s="3">
         <v>115600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>110900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>102200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>93500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>90100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>80800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>72900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>63400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>164100</v>
-      </c>
-      <c r="N76" s="3">
-        <v>150300</v>
       </c>
       <c r="O76" s="3">
         <v>150300</v>
       </c>
       <c r="P76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="Q76" s="3">
         <v>143900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>148500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>144400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>143200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>140900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>138600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>136600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>140800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>137600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>138700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>131200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>129700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>123600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>128400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>121600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>115400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>107300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>98100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>91800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>86300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E80" s="2">
         <v>45653</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45562</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45471</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45380</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45289</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45198</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44925</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44743</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44652</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44470</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44379</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44288</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44197</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44099</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44008</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43917</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43826</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43644</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43553</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43462</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43371</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43280</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43189</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43098</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43007</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42734</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>8700</v>
       </c>
       <c r="G81" s="3">
         <v>8700</v>
       </c>
       <c r="H81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I81" s="3">
         <v>7900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>6200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7997,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7811,7 +8010,7 @@
         <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
@@ -7835,16 +8034,16 @@
         <v>800</v>
       </c>
       <c r="N83" s="3">
+        <v>800</v>
+      </c>
+      <c r="O83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1100</v>
       </c>
       <c r="R83" s="3">
         <v>1100</v>
@@ -7853,19 +8052,19 @@
         <v>1100</v>
       </c>
       <c r="T83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="U83" s="3">
         <v>1200</v>
       </c>
       <c r="V83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W83" s="3">
         <v>1100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>1100</v>
       </c>
       <c r="Y83" s="3">
         <v>1100</v>
@@ -7874,10 +8073,10 @@
         <v>1100</v>
       </c>
       <c r="AA83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>900</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>1200</v>
       </c>
       <c r="AC83" s="3">
         <v>1200</v>
@@ -7892,22 +8091,25 @@
         <v>1200</v>
       </c>
       <c r="AG83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AH83" s="3">
         <v>1100</v>
       </c>
       <c r="AI83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>900</v>
       </c>
       <c r="AK83" s="3">
         <v>900</v>
       </c>
+      <c r="AL83" s="3">
+        <v>900</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>20600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>25600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>24800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>24300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>15800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>17200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>12100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,19 +8807,20 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-900</v>
       </c>
       <c r="G91" s="3">
         <v>-900</v>
@@ -8608,7 +8829,7 @@
         <v>-900</v>
       </c>
       <c r="I91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="J91" s="3">
         <v>-1100</v>
@@ -8617,13 +8838,13 @@
         <v>-1100</v>
       </c>
       <c r="L91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-1000</v>
       </c>
       <c r="O91" s="3">
         <v>-1000</v>
@@ -8632,70 +8853,73 @@
         <v>-1000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,19 +9135,22 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-900</v>
       </c>
       <c r="G94" s="3">
         <v>-900</v>
@@ -8929,7 +9159,7 @@
         <v>-900</v>
       </c>
       <c r="I94" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="J94" s="3">
         <v>-1100</v>
@@ -8938,85 +9168,88 @@
         <v>-1100</v>
       </c>
       <c r="L94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-1000</v>
       </c>
       <c r="P94" s="3">
         <v>-1000</v>
       </c>
       <c r="Q94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9287,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9084,7 +9318,7 @@
         <v>3000</v>
       </c>
       <c r="L96" s="3">
-        <v>-3500</v>
+        <v>3000</v>
       </c>
       <c r="M96" s="3">
         <v>-3500</v>
@@ -9093,76 +9327,79 @@
         <v>-3500</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-6100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-5800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,115 +9725,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-60100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9652,35 +9901,35 @@
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -9696,111 +9945,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E102" s="3">
         <v>6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>5400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,493 +656,506 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E7" s="2">
         <v>45744</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45653</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45562</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45471</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45380</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45289</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45198</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44925</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44743</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44652</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44470</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44379</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44288</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44197</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44099</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43917</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43826</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43644</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43553</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43462</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43371</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43280</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43189</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43098</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43007</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42734</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E8" s="3">
         <v>76200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>77500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>77900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>75700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>74600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>75600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>69800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>70100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>72000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>75700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>70200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>71900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>73200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>59300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>57900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>52800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>69500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>69100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>72700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>73500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>67200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>63700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>73700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>74500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>71100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>60100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>71500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>73600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>71400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>70100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E9" s="3">
         <v>48400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>45400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>45800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>41900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>44400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>45400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>40500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>45900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>47900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>42700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>45700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>43400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>41200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>38900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>39700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>47100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>45400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>48300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>47500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>44600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>40100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>49600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>49200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>48300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>38600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>47800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>49200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>48300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>45600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E10" s="3">
         <v>27900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>31500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>29300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>30200</v>
       </c>
       <c r="K10" s="3">
         <v>30200</v>
       </c>
       <c r="L10" s="3">
+        <v>30200</v>
+      </c>
+      <c r="M10" s="3">
         <v>26700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>29600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>30000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>27500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>29800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>20400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>18200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>12100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>24400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>26000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>22600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>25300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>22800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>23700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>24400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>23100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>24500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1194,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1291,8 +1305,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,55 +1418,58 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1457,73 +1477,76 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>5500</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>5000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>4400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>100</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>900</v>
       </c>
       <c r="G15" s="3">
         <v>900</v>
@@ -1538,13 +1561,13 @@
         <v>900</v>
       </c>
       <c r="K15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L15" s="3">
         <v>800</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1561,8 +1584,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
@@ -1579,12 +1602,12 @@
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="3">
         <v>200</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1597,8 +1620,8 @@
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1621,8 +1644,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1684,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E17" s="3">
         <v>71800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>69700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>65100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>63400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>64100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>58500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>60900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>62900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>58600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>56500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>58000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>61700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>58200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>60500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>59000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>54600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>57800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>53400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>57800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>61800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>65500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>63800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>58600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>60100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>65500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>60300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>62800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>53700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>63600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>67100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>63500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>60400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E18" s="3">
         <v>4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>7900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>9700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,8 +1951,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1950,8 +1984,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -2028,154 +2062,160 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E21" s="3">
         <v>5600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>16000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>10500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>10800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>15500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>10600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
       </c>
       <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>500</v>
       </c>
       <c r="H22" s="3">
         <v>500</v>
       </c>
       <c r="I22" s="3">
+        <v>500</v>
+      </c>
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>900</v>
       </c>
       <c r="L22" s="3">
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>900</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -2210,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>100</v>
@@ -2222,7 +2262,7 @@
         <v>100</v>
       </c>
       <c r="AD22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE22" s="3">
         <v>200</v>
@@ -2237,7 +2277,7 @@
         <v>200</v>
       </c>
       <c r="AI22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ22" s="3">
         <v>100</v>
@@ -2248,8 +2288,11 @@
       <c r="AL22" s="3">
         <v>100</v>
       </c>
+      <c r="AM22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2257,219 +2300,225 @@
         <v>4200</v>
       </c>
       <c r="E23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F23" s="3">
         <v>7500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>14100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>9600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>2400</v>
       </c>
       <c r="AE24" s="3">
         <v>2400</v>
       </c>
       <c r="AF24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AG24" s="3">
         <v>800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
         <v>3300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2627,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>8700</v>
       </c>
       <c r="H26" s="3">
         <v>8700</v>
       </c>
       <c r="I26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J26" s="3">
         <v>7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6900</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>7000</v>
       </c>
       <c r="AB26" s="3">
         <v>7000</v>
       </c>
       <c r="AC26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AD26" s="3">
         <v>3300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>11700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>7900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>6200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>8700</v>
       </c>
       <c r="H27" s="3">
         <v>8700</v>
       </c>
       <c r="I27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J27" s="3">
         <v>7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6900</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>7000</v>
       </c>
       <c r="AB27" s="3">
         <v>7000</v>
       </c>
       <c r="AC27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AD27" s="3">
         <v>3300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>7900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>6200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2966,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2968,11 +3029,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2983,29 +3044,29 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-100</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-500</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-200</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>5800</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3018,8 +3079,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3192,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,8 +3305,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3270,8 +3340,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3348,118 +3418,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>8700</v>
       </c>
       <c r="H33" s="3">
         <v>8700</v>
       </c>
       <c r="I33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J33" s="3">
         <v>7900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>7900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>6200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3644,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>8700</v>
       </c>
       <c r="H35" s="3">
         <v>8700</v>
       </c>
       <c r="I35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J35" s="3">
         <v>7900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>7900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>6200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E38" s="2">
         <v>45744</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45653</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45562</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45471</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45380</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45289</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45198</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44925</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44743</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44652</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44470</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44379</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44288</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44197</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44099</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43917</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43826</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43644</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43553</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43462</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43371</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43280</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43189</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43098</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43007</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42734</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3918,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,118 +3959,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E41" s="3">
         <v>9200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>67000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>47800</v>
       </c>
       <c r="P41" s="3">
         <v>47800</v>
       </c>
       <c r="Q41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="R41" s="3">
         <v>45800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>51100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>23300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>23700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>17500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>16200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>17100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>19700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4093,118 +4183,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E43" s="3">
         <v>62600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>57100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>58000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>52100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>62200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>57800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>52000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>48400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52100</v>
-      </c>
-      <c r="O43" s="3">
-        <v>50500</v>
       </c>
       <c r="P43" s="3">
         <v>50500</v>
       </c>
       <c r="Q43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="R43" s="3">
         <v>50600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>49600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>47200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>38500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>32800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>36200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>37000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>53400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>49800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>57900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>54500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>56000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>54800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>56900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>56800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>51900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>52300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>55600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>50400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>49900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>47400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4235,8 +4331,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4313,8 +4409,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4345,196 +4444,202 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>5400</v>
       </c>
       <c r="P45" s="3">
         <v>5400</v>
       </c>
       <c r="Q45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="R45" s="3">
         <v>5800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E46" s="3">
         <v>75000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>76300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>74900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>80300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>73700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>75400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>75300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>72000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>81200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>122400</v>
-      </c>
-      <c r="O46" s="3">
-        <v>103600</v>
       </c>
       <c r="P46" s="3">
         <v>103600</v>
       </c>
       <c r="Q46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="R46" s="3">
         <v>102200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>105700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>102300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>92400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>84800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>82700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>78100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>80000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>78600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>78000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>75300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>70700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>73100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>73800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>73300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>79100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>75300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>74700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>68000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>69600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>68800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4565,8 +4670,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4643,228 +4748,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E48" s="3">
         <v>24000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19500</v>
-      </c>
-      <c r="O48" s="3">
-        <v>19600</v>
       </c>
       <c r="P48" s="3">
         <v>19600</v>
       </c>
       <c r="Q48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="R48" s="3">
         <v>19700</v>
       </c>
       <c r="S48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="T48" s="3">
         <v>19900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>28500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>29100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>29400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>28700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>28900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>24300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>22800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>15800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E49" s="3">
         <v>92400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>92100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>92200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>84100</v>
       </c>
       <c r="H49" s="3">
         <v>84100</v>
       </c>
       <c r="I49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="J49" s="3">
         <v>84200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>83700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>84100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>83800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>83500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>82500</v>
-      </c>
-      <c r="O49" s="3">
-        <v>84600</v>
       </c>
       <c r="P49" s="3">
         <v>84600</v>
       </c>
       <c r="Q49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="R49" s="3">
         <v>85100</v>
       </c>
       <c r="S49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="T49" s="3">
         <v>85400</v>
       </c>
       <c r="U49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="V49" s="3">
         <v>85300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>84300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>83900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>83800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>83800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>84200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>84600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>84700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>85700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>85100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>85000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>85300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>72600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>72400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5087,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,8 +5200,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5101,7 +5221,7 @@
         <v>400</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
@@ -5122,79 +5242,82 @@
         <v>300</v>
       </c>
       <c r="O52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>500</v>
       </c>
       <c r="Q52" s="3">
+        <v>500</v>
+      </c>
+      <c r="R52" s="3">
         <v>600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5426,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>200500</v>
+      </c>
+      <c r="E54" s="3">
         <v>191800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>191900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>190800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>187500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>179300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>181400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>180800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>182900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>177700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>185000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>224700</v>
-      </c>
-      <c r="O54" s="3">
-        <v>208400</v>
       </c>
       <c r="P54" s="3">
         <v>208400</v>
       </c>
       <c r="Q54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="R54" s="3">
         <v>207500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>211400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>208800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>199400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>192500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>196100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>192500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>195100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>193700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>193900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>191400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>187700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>180800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>187100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>185900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>191000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>185200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>182200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>174900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>160800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>159300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5582,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,118 +5623,122 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
-      </c>
-      <c r="O57" s="3">
-        <v>8000</v>
       </c>
       <c r="P57" s="3">
         <v>8000</v>
       </c>
       <c r="Q57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="R57" s="3">
         <v>7700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5612,31 +5746,31 @@
         <v>1200</v>
       </c>
       <c r="E58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1200</v>
       </c>
       <c r="L58" s="3">
         <v>1200</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -5713,264 +5847,273 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E59" s="3">
         <v>23300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>50900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>47300</v>
-      </c>
-      <c r="O59" s="3">
-        <v>39900</v>
       </c>
       <c r="P59" s="3">
         <v>39900</v>
       </c>
       <c r="Q59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="R59" s="3">
         <v>47200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>50900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>41200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>36500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>40100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>37500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>30500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>35200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>34200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>35500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>30200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>36800</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>34100</v>
       </c>
       <c r="AE59" s="3">
         <v>34100</v>
       </c>
       <c r="AF59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AG59" s="3">
         <v>39800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>43000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>36000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>37100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>34200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>46700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E60" s="3">
         <v>47200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>46800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>49900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51900</v>
-      </c>
-      <c r="O60" s="3">
-        <v>48000</v>
       </c>
       <c r="P60" s="3">
         <v>48000</v>
       </c>
       <c r="Q60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="R60" s="3">
         <v>54900</v>
       </c>
       <c r="S60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="T60" s="3">
         <v>55600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>46200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>42600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>45100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>42300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>43700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>39400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>42300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>36600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>44200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>39200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>42500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>48400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>51400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>44600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>45200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>45800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>55800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E61" s="3">
         <v>19700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>59100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>59700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -6005,46 +6148,49 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>2500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>19000</v>
       </c>
       <c r="AG61" s="3">
         <v>19000</v>
       </c>
       <c r="AH61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>22000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6075,86 +6221,89 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>7500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8600</v>
-      </c>
-      <c r="O62" s="3">
-        <v>10200</v>
       </c>
       <c r="P62" s="3">
         <v>10200</v>
       </c>
       <c r="Q62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R62" s="3">
         <v>8800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>10200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6412,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6525,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6638,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E66" s="3">
         <v>77300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>76300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>79800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>91300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>110000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>114200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>126700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>60600</v>
-      </c>
-      <c r="O66" s="3">
-        <v>58100</v>
       </c>
       <c r="P66" s="3">
         <v>58100</v>
       </c>
       <c r="Q66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="R66" s="3">
         <v>63700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>62900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>57500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>55900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>54300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>56100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>55200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>60200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>57200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>58700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>75700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>78000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>84100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>83100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>64700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>73000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6794,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6905,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7018,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7131,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7244,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E72" s="3">
         <v>78100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>78300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>77800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>72200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>66500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>60800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>43800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31900</v>
-      </c>
-      <c r="O72" s="3">
-        <v>18300</v>
       </c>
       <c r="P72" s="3">
         <v>18300</v>
       </c>
       <c r="Q72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="R72" s="3">
         <v>11300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-15200</v>
       </c>
       <c r="W72" s="3">
         <v>-15200</v>
       </c>
       <c r="X72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-18300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-25400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-19900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7470,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7583,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7696,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E76" s="3">
         <v>114400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>115600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>110900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>102200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>93500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>90100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>80800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>72900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>63400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>58300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>164100</v>
-      </c>
-      <c r="O76" s="3">
-        <v>150300</v>
       </c>
       <c r="P76" s="3">
         <v>150300</v>
       </c>
       <c r="Q76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="R76" s="3">
         <v>143900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>148500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>144400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>143200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>140900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>138600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>136600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>140800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>137600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>138700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>131200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>129700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>123600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>128400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>121600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>115400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>107300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>98100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>91800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>96000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>86300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7922,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E80" s="2">
         <v>45744</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45653</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45562</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45471</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45380</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45289</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45198</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44925</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44743</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44652</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44470</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44379</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44288</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44197</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44099</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43917</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43826</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43644</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43553</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43462</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43371</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43280</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43189</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43098</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43007</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42734</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>8700</v>
       </c>
       <c r="H81" s="3">
         <v>8700</v>
       </c>
       <c r="I81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J81" s="3">
         <v>7900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>7900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>6200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,8 +8196,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8013,7 +8212,7 @@
         <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -8037,16 +8236,16 @@
         <v>800</v>
       </c>
       <c r="O83" s="3">
+        <v>800</v>
+      </c>
+      <c r="P83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1100</v>
       </c>
       <c r="S83" s="3">
         <v>1100</v>
@@ -8055,19 +8254,19 @@
         <v>1100</v>
       </c>
       <c r="U83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="V83" s="3">
         <v>1200</v>
       </c>
       <c r="W83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X83" s="3">
         <v>1100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>1100</v>
       </c>
       <c r="Z83" s="3">
         <v>1100</v>
@@ -8076,10 +8275,10 @@
         <v>1100</v>
       </c>
       <c r="AB83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC83" s="3">
         <v>900</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>1200</v>
       </c>
       <c r="AD83" s="3">
         <v>1200</v>
@@ -8094,22 +8293,25 @@
         <v>1200</v>
       </c>
       <c r="AH83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AI83" s="3">
         <v>1100</v>
       </c>
       <c r="AJ83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AK83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>900</v>
       </c>
       <c r="AL83" s="3">
         <v>900</v>
       </c>
+      <c r="AM83" s="3">
+        <v>900</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8420,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8533,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8646,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8759,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8872,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>4200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>20600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>25600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>24800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>24300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>19900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>17200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>12100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,22 +9028,23 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-900</v>
       </c>
       <c r="H91" s="3">
         <v>-900</v>
@@ -8832,7 +9053,7 @@
         <v>-900</v>
       </c>
       <c r="J91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="K91" s="3">
         <v>-1100</v>
@@ -8841,13 +9062,13 @@
         <v>-1100</v>
       </c>
       <c r="M91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-900</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-1000</v>
       </c>
       <c r="P91" s="3">
         <v>-1000</v>
@@ -8856,70 +9077,73 @@
         <v>-1000</v>
       </c>
       <c r="R91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9252,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,22 +9365,25 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-900</v>
       </c>
       <c r="H94" s="3">
         <v>-900</v>
@@ -9162,7 +9392,7 @@
         <v>-900</v>
       </c>
       <c r="J94" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="K94" s="3">
         <v>-1100</v>
@@ -9171,85 +9401,88 @@
         <v>-1100</v>
       </c>
       <c r="M94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q94" s="3">
         <v>-1000</v>
       </c>
       <c r="R94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,13 +9521,14 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="E96" s="3">
         <v>3000</v>
@@ -9321,7 +9555,7 @@
         <v>3000</v>
       </c>
       <c r="M96" s="3">
-        <v>-3500</v>
+        <v>3000</v>
       </c>
       <c r="N96" s="3">
         <v>-3500</v>
@@ -9330,76 +9564,79 @@
         <v>-3500</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-6400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-6100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9745,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9858,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,118 +9971,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-60100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-26000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9904,35 +10153,35 @@
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
         <v>0</v>
       </c>
@@ -9948,114 +10197,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-36800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>5400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,519 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46017</v>
+      </c>
+      <c r="E7" s="2">
         <v>45926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45835</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45744</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45653</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45562</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45471</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45380</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45289</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45198</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44925</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44743</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44652</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44470</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44379</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44288</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44197</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44099</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44008</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43917</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43826</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43644</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43553</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43462</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43371</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43280</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43189</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43098</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43007</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42734</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E8" s="3">
         <v>72200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>77600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>76200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>77500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>77900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>71200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>74600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>75600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>69800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>70100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>72000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>75900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>75700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>70200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>71900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>73200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>63500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>59300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>57900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>52800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>69500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>69100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>72700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>73500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>67200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>63700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>73700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>74500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>71100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>71500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>73600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>71400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>70100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E9" s="3">
         <v>42400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>48400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>46200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>46400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>41900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>44400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>43900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>45900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>47900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>42700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>45700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>43400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>41200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>38900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>39700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>40700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>47100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>45400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>48300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>47500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>44600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>40100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>49600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>49200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>48300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>38600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>47800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>49200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>48300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>45600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E10" s="3">
         <v>29700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>30500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29300</v>
-      </c>
-      <c r="L10" s="3">
-        <v>30200</v>
       </c>
       <c r="M10" s="3">
         <v>30200</v>
       </c>
       <c r="N10" s="3">
+        <v>30200</v>
+      </c>
+      <c r="O10" s="3">
         <v>26700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>29600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>30000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>27800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>27500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>29800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>20400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>26000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>22600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>23600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>24100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>25300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>22800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>21500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>23700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>24400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>23100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>24500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1209,8 +1221,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1325,8 +1338,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1441,61 +1457,64 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1503,62 +1522,65 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>5500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>5000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>4400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>100</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1566,16 +1588,16 @@
         <v>1400</v>
       </c>
       <c r="E15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F15" s="3">
         <v>1300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>900</v>
       </c>
       <c r="I15" s="3">
         <v>900</v>
@@ -1590,13 +1612,13 @@
         <v>900</v>
       </c>
       <c r="M15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N15" s="3">
         <v>800</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1613,8 +1635,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
@@ -1631,12 +1653,12 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB15" s="3">
         <v>200</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1649,8 +1671,8 @@
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1673,8 +1695,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1712,240 +1737,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E17" s="3">
         <v>63600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>73000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>69700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>65100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>63400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>64100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>60900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>62900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>58600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>58000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>61700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>62300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>58200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>60500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>59000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>54600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>57800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>57800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>61800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>65500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>63300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>63800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>58600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>60100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>65500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>60300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>62800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>63600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>67100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>63500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>60400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E18" s="3">
         <v>8600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>14200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>7900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>7900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>9700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1986,8 +2018,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2024,8 +2057,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -2102,166 +2135,172 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E21" s="3">
         <v>9900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>15300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>10500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>10800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>15500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>7600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>9000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>10600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
         <v>400</v>
       </c>
       <c r="F22" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>500</v>
       </c>
       <c r="J22" s="3">
         <v>500</v>
       </c>
       <c r="K22" s="3">
+        <v>500</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>900</v>
       </c>
       <c r="N22" s="3">
         <v>900</v>
       </c>
       <c r="O22" s="3">
+        <v>900</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2296,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
@@ -2308,7 +2347,7 @@
         <v>100</v>
       </c>
       <c r="AF22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG22" s="3">
         <v>200</v>
@@ -2323,7 +2362,7 @@
         <v>200</v>
       </c>
       <c r="AK22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL22" s="3">
         <v>100</v>
@@ -2334,240 +2373,249 @@
       <c r="AN22" s="3">
         <v>100</v>
       </c>
+      <c r="AO22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E23" s="3">
         <v>5000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>4200</v>
       </c>
       <c r="F23" s="3">
         <v>4200</v>
       </c>
       <c r="G23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H23" s="3">
         <v>7500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>14100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>6300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>7900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>9600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>2400</v>
       </c>
       <c r="AG24" s="3">
         <v>2400</v>
       </c>
       <c r="AH24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AI24" s="3">
         <v>800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1600</v>
       </c>
-      <c r="AL24" s="3">
-        <v>0</v>
-      </c>
       <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
         <v>3300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2682,240 +2730,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>8700</v>
       </c>
       <c r="J26" s="3">
         <v>8700</v>
       </c>
       <c r="K26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L26" s="3">
         <v>7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6900</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>7000</v>
       </c>
       <c r="AD26" s="3">
         <v>7000</v>
       </c>
       <c r="AE26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AF26" s="3">
         <v>3300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>11700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>7300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>7900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>6200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>8700</v>
       </c>
       <c r="J27" s="3">
         <v>8700</v>
       </c>
       <c r="K27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L27" s="3">
         <v>7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6900</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>7000</v>
       </c>
       <c r="AD27" s="3">
         <v>7000</v>
       </c>
       <c r="AE27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AF27" s="3">
         <v>3300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>11700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>5300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>7900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>6200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3030,8 +3087,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3096,11 +3156,11 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
@@ -3111,29 +3171,29 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-100</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-500</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3146,8 +3206,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3262,8 +3325,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3378,8 +3444,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3416,8 +3485,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3494,124 +3563,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E33" s="3">
         <v>2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>8700</v>
       </c>
       <c r="J33" s="3">
         <v>8700</v>
       </c>
       <c r="K33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L33" s="3">
         <v>7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>11500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>5300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>7900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>6200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3726,245 +3801,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E35" s="3">
         <v>2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>8700</v>
       </c>
       <c r="J35" s="3">
         <v>8700</v>
       </c>
       <c r="K35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L35" s="3">
         <v>7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>11500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>5300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>7900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>6200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46017</v>
+      </c>
+      <c r="E38" s="2">
         <v>45926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45835</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45744</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45653</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45562</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45471</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45380</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45289</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45198</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44925</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44743</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44652</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44470</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44379</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44288</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44197</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44099</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44008</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43917</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43826</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43644</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43553</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43462</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43371</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43280</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43189</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43098</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43007</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42734</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4005,8 +4089,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4047,124 +4132,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E41" s="3">
         <v>13900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>67000</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>47800</v>
       </c>
       <c r="R41" s="3">
         <v>47800</v>
       </c>
       <c r="S41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="T41" s="3">
         <v>45800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>52900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>52500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>37400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>26000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>23700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>16200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>14400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>17100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>19700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4279,124 +4368,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E43" s="3">
         <v>57300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>63400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>62600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>57100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>58100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>62200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>57800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>48400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>52100</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>50500</v>
       </c>
       <c r="R43" s="3">
         <v>50500</v>
       </c>
       <c r="S43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="T43" s="3">
         <v>50600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>47200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>38500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>36200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>37000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>53400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>49800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>57900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>54500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>56000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>54800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>56900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>56800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>51900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>52300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>55600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>50400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>49900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>47400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4433,8 +4528,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4511,8 +4606,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4549,202 +4647,208 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>2500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>5400</v>
       </c>
       <c r="R45" s="3">
         <v>5400</v>
       </c>
       <c r="S45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="T45" s="3">
         <v>5800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E46" s="3">
         <v>80400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>80200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>76300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>74900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>80300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>73700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>75400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>76800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>72000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>81200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>122400</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>103600</v>
       </c>
       <c r="R46" s="3">
         <v>103600</v>
       </c>
       <c r="S46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="T46" s="3">
         <v>102200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>105700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>102300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>92400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>84800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>82700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>78100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>80000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>78600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>78000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>75300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>70700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>73100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>73800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>73300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>79100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>75300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>74700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>68000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>69600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>68800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4781,8 +4885,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4859,240 +4963,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E48" s="3">
         <v>25800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>19600</v>
       </c>
       <c r="R48" s="3">
         <v>19600</v>
       </c>
       <c r="S48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="T48" s="3">
         <v>19700</v>
       </c>
       <c r="U48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="V48" s="3">
         <v>19900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>28500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>29100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>27900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>29400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>28700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>28900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>24300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>22800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>20700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>16500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>15800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>14800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E49" s="3">
         <v>94100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>95200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>92400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>92100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>92200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>84100</v>
       </c>
       <c r="J49" s="3">
         <v>84100</v>
       </c>
       <c r="K49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="L49" s="3">
         <v>84200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>83700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>83800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>83500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>82500</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>84600</v>
       </c>
       <c r="R49" s="3">
         <v>84600</v>
       </c>
       <c r="S49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="T49" s="3">
         <v>85100</v>
       </c>
       <c r="U49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="V49" s="3">
         <v>85400</v>
       </c>
       <c r="W49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="X49" s="3">
         <v>85300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>84300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>83900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>83800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>83800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>84200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>84600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>84200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>84600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>84700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>85700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>85100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>85000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>85300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>72600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>72400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5207,8 +5320,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5323,8 +5439,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5347,7 +5466,7 @@
         <v>400</v>
       </c>
       <c r="J52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
@@ -5368,79 +5487,82 @@
         <v>300</v>
       </c>
       <c r="Q52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="R52" s="3">
         <v>500</v>
       </c>
       <c r="S52" s="3">
+        <v>500</v>
+      </c>
+      <c r="T52" s="3">
         <v>600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>3300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5555,124 +5677,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>206400</v>
+      </c>
+      <c r="E54" s="3">
         <v>200700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>200500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>191800</v>
       </c>
-      <c r="G54" s="3">
-        <v>191900</v>
-      </c>
       <c r="H54" s="3">
+        <v>193300</v>
+      </c>
+      <c r="I54" s="3">
         <v>190800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>187500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>179300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>181400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>180800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>182900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>177700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>185000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>224700</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>208400</v>
       </c>
       <c r="R54" s="3">
         <v>208400</v>
       </c>
       <c r="S54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="T54" s="3">
         <v>207500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>211400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>208800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>199400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>192500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>196100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>192500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>195100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>193700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>193900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>191400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>187700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>180800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>187100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>185900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>191000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>182200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>174900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>160800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>159300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5713,8 +5841,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5755,129 +5884,133 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>8000</v>
       </c>
       <c r="R57" s="3">
         <v>8000</v>
       </c>
       <c r="S57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T57" s="3">
         <v>7700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>11700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>9100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
         <v>1200</v>
@@ -5886,31 +6019,31 @@
         <v>1200</v>
       </c>
       <c r="G58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1300</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1200</v>
       </c>
       <c r="N58" s="3">
         <v>1200</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5987,282 +6120,291 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E59" s="3">
         <v>18800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>50900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>47300</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>39900</v>
       </c>
       <c r="R59" s="3">
         <v>39900</v>
       </c>
       <c r="S59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="T59" s="3">
         <v>47200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>50900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>41200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>36500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>40100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>37500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>30500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>35200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>34200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>35500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>30200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>36800</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>34100</v>
       </c>
       <c r="AG59" s="3">
         <v>34100</v>
       </c>
       <c r="AH59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AI59" s="3">
         <v>39800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>36000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>37100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>34200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>46700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E60" s="3">
         <v>42700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>47000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>49500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>44300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>49900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>47000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>51900</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>48000</v>
       </c>
       <c r="R60" s="3">
         <v>48000</v>
       </c>
       <c r="S60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="T60" s="3">
         <v>54900</v>
       </c>
       <c r="U60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="V60" s="3">
         <v>55600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>46200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>42600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>45100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>42300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>43700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>39400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>42300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>36600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>44200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>39200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>42500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>48400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>51400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>44600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>45200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>45800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>55800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E61" s="3">
         <v>45300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>24500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>33300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>53800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>59100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>59700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6297,46 +6439,49 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>2500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>19000</v>
       </c>
       <c r="AI61" s="3">
         <v>19000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>22000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>20000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>9000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6373,86 +6518,89 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3">
         <v>7500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>10200</v>
       </c>
       <c r="R62" s="3">
         <v>10200</v>
       </c>
       <c r="S62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="T62" s="3">
         <v>8800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>8200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>17500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>17800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>9900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>10200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6567,8 +6715,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6683,8 +6834,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6799,124 +6953,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>138300</v>
+      </c>
+      <c r="E66" s="3">
         <v>99000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77300</v>
       </c>
-      <c r="G66" s="3">
-        <v>76300</v>
-      </c>
       <c r="H66" s="3">
+        <v>77700</v>
+      </c>
+      <c r="I66" s="3">
         <v>79800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>85300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>85800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>91300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>110000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>114200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>126700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60600</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>58100</v>
       </c>
       <c r="R66" s="3">
         <v>58100</v>
       </c>
       <c r="S66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="T66" s="3">
         <v>63700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>62900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>56200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>55900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>54300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>56100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>55200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>60200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>57900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>57200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>58700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>64300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>75700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>78000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>84100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>83100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>64700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>73000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6957,8 +7117,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7073,8 +7234,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7189,8 +7353,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7305,8 +7472,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7421,124 +7591,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E72" s="3">
         <v>75800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>76500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>78100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>78300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>77800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>72200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>66500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>60800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>31900</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>18300</v>
       </c>
       <c r="R72" s="3">
         <v>18300</v>
       </c>
       <c r="S72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="T72" s="3">
         <v>11300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-14300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-15200</v>
       </c>
       <c r="Y72" s="3">
         <v>-15200</v>
       </c>
       <c r="Z72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-13700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-18300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-25400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-19900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7653,8 +7829,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7769,8 +7948,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7885,124 +8067,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E76" s="3">
         <v>101600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>119800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>114400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>115600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>110900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>102200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>93500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>90100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>80800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>72900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>63400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>164100</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>150300</v>
       </c>
       <c r="R76" s="3">
         <v>150300</v>
       </c>
       <c r="S76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="T76" s="3">
         <v>143900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>148500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>144400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>143200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>140900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>138600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>136600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>140800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>137600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>138700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>131200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>129700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>123600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>128400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>121600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>115400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>107300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>98100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>91800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>96000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>86300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8117,245 +8305,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46017</v>
+      </c>
+      <c r="E80" s="2">
         <v>45926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45835</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45744</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45653</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45562</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45471</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45380</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45289</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45198</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44925</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44743</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44652</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44470</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44379</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44288</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44197</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44099</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44008</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43917</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43826</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43644</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43553</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43462</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43371</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43280</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43189</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43098</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43007</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42734</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E81" s="3">
         <v>2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>8700</v>
       </c>
       <c r="J81" s="3">
         <v>8700</v>
       </c>
       <c r="K81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L81" s="3">
         <v>7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>11500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>5300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>7900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>6200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8396,8 +8593,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8417,7 +8615,7 @@
         <v>900</v>
       </c>
       <c r="I83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J83" s="3">
         <v>800</v>
@@ -8441,16 +8639,16 @@
         <v>800</v>
       </c>
       <c r="Q83" s="3">
+        <v>800</v>
+      </c>
+      <c r="R83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1100</v>
       </c>
       <c r="U83" s="3">
         <v>1100</v>
@@ -8459,19 +8657,19 @@
         <v>1100</v>
       </c>
       <c r="W83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="X83" s="3">
         <v>1200</v>
       </c>
       <c r="Y83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>1100</v>
       </c>
       <c r="AB83" s="3">
         <v>1100</v>
@@ -8480,10 +8678,10 @@
         <v>1100</v>
       </c>
       <c r="AD83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>900</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>1200</v>
       </c>
       <c r="AF83" s="3">
         <v>1200</v>
@@ -8498,22 +8696,25 @@
         <v>1200</v>
       </c>
       <c r="AJ83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AK83" s="3">
         <v>1100</v>
       </c>
       <c r="AL83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AM83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>900</v>
       </c>
       <c r="AN83" s="3">
         <v>900</v>
       </c>
+      <c r="AO83" s="3">
+        <v>900</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8628,8 +8829,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8744,8 +8948,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8860,8 +9067,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8976,8 +9186,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9092,124 +9305,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E89" s="3">
         <v>11400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>24800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>24300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>13800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>10100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>14500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>9500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>17200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>10000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>12100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9250,28 +9469,29 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-900</v>
       </c>
       <c r="J91" s="3">
         <v>-900</v>
@@ -9280,7 +9500,7 @@
         <v>-900</v>
       </c>
       <c r="L91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="M91" s="3">
         <v>-1100</v>
@@ -9289,13 +9509,13 @@
         <v>-1100</v>
       </c>
       <c r="O91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-1000</v>
       </c>
       <c r="R91" s="3">
         <v>-1000</v>
@@ -9304,70 +9524,73 @@
         <v>-1000</v>
       </c>
       <c r="T91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9482,8 +9705,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9598,28 +9824,31 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7800</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-900</v>
       </c>
       <c r="J94" s="3">
         <v>-900</v>
@@ -9628,7 +9857,7 @@
         <v>-900</v>
       </c>
       <c r="L94" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="M94" s="3">
         <v>-1100</v>
@@ -9637,85 +9866,88 @@
         <v>-1100</v>
       </c>
       <c r="O94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-1000</v>
       </c>
       <c r="S94" s="3">
         <v>-1000</v>
       </c>
       <c r="T94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9756,8 +9988,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9768,7 +10001,7 @@
         <v>3300</v>
       </c>
       <c r="F96" s="3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="G96" s="3">
         <v>3000</v>
@@ -9795,7 +10028,7 @@
         <v>3000</v>
       </c>
       <c r="O96" s="3">
-        <v>-3500</v>
+        <v>3000</v>
       </c>
       <c r="P96" s="3">
         <v>-3500</v>
@@ -9804,76 +10037,79 @@
         <v>-3500</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-6400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-6100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9988,8 +10224,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10104,8 +10343,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10220,124 +10462,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-60100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-26000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>3600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10408,35 +10656,35 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
@@ -10452,120 +10700,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-36800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>5400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCKT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
   <si>
     <t>HCKT</t>
   </si>
@@ -656,531 +656,544 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E7" s="2">
         <v>46017</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45835</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45744</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45653</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45562</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45471</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45380</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45289</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45198</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44925</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44743</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44652</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44470</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44379</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44288</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44197</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44099</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44008</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43917</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43826</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43644</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43553</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43462</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43371</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43280</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43189</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43098</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43007</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42734</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E8" s="3">
         <v>74800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>72200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>77600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>76200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>77500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>77900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>75700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>74600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>69800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>72000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>75900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>75700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>70200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>71900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>73200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>63500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>59300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>57900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>52800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>69500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>69100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>72700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>73500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>67200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>63700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>73700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>74500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>60100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>71500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>73600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>71400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>70100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E9" s="3">
         <v>43200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>48400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>46200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>46400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>45800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>44400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>43100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>40500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>43900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>45900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>42700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>45700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>43400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>41200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>38900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>39700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>40700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>47100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>45400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>48300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>47500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>44600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>40100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>49600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>49200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>38600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>47800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>49200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>48300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>45600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E10" s="3">
         <v>31600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>27900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29300</v>
-      </c>
-      <c r="M10" s="3">
-        <v>30200</v>
       </c>
       <c r="N10" s="3">
         <v>30200</v>
       </c>
       <c r="O10" s="3">
+        <v>30200</v>
+      </c>
+      <c r="P10" s="3">
         <v>26700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>30000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>27800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>27500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>29800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>20400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>12100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>26000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>22600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>23600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>24100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>25300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>22800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>21500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>23700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>24400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>23100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>24500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,8 +1235,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1341,8 +1355,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,64 +1477,67 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>3100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1525,82 +1545,85 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>5500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>5000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>4400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-100</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>1900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>100</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
         <v>1400</v>
       </c>
       <c r="F15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>900</v>
       </c>
       <c r="J15" s="3">
         <v>900</v>
@@ -1615,13 +1638,13 @@
         <v>900</v>
       </c>
       <c r="N15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="O15" s="3">
         <v>800</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1638,8 +1661,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
@@ -1656,12 +1679,12 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="3">
         <v>200</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1674,8 +1697,8 @@
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH15" s="3">
-        <v>0</v>
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI15" s="3">
         <v>0</v>
@@ -1698,8 +1721,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1764,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E17" s="3">
         <v>65700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>63600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>73000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>69700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>65100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>63400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>64100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>58500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>60900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>62900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>58600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>58000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>61700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>62300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>58200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>60500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>59000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>54600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>57800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>53400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>57800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>61800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>65500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>63300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>63800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>58600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>60100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>65500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>60300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>62800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>53700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>63600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>67100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>63500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>60400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E18" s="3">
         <v>9100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>14200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>7900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>6500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>7900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>9700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,8 +2052,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2060,8 +2094,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2138,172 +2172,178 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E21" s="3">
         <v>10500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>15300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>10500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>15500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>9000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>9000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>10600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
-      </c>
-      <c r="E22" s="3">
-        <v>400</v>
       </c>
       <c r="F22" s="3">
         <v>400</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>500</v>
       </c>
       <c r="K22" s="3">
         <v>500</v>
       </c>
       <c r="L22" s="3">
+        <v>500</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>900</v>
       </c>
       <c r="O22" s="3">
         <v>900</v>
       </c>
       <c r="P22" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2338,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="3">
         <v>100</v>
@@ -2350,7 +2390,7 @@
         <v>100</v>
       </c>
       <c r="AG22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH22" s="3">
         <v>200</v>
@@ -2365,7 +2405,7 @@
         <v>200</v>
       </c>
       <c r="AL22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AM22" s="3">
         <v>100</v>
@@ -2376,246 +2416,255 @@
       <c r="AO22" s="3">
         <v>100</v>
       </c>
+      <c r="AP22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E23" s="3">
         <v>8400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>4200</v>
       </c>
       <c r="G23" s="3">
         <v>4200</v>
       </c>
       <c r="H23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I23" s="3">
         <v>7500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>14100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>7700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>6300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>7900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>9600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>2400</v>
       </c>
       <c r="AH24" s="3">
         <v>2400</v>
       </c>
       <c r="AI24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1600</v>
       </c>
-      <c r="AM24" s="3">
-        <v>0</v>
-      </c>
       <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
         <v>3300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,246 +2782,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E26" s="3">
         <v>5600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>8700</v>
       </c>
       <c r="K26" s="3">
         <v>8700</v>
       </c>
       <c r="L26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="M26" s="3">
         <v>7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6900</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>7000</v>
       </c>
       <c r="AE26" s="3">
         <v>7000</v>
       </c>
       <c r="AF26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AG26" s="3">
         <v>3300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>11700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>7900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>6200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E27" s="3">
         <v>5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>8700</v>
       </c>
       <c r="K27" s="3">
         <v>8700</v>
       </c>
       <c r="L27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="M27" s="3">
         <v>7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6900</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>7000</v>
       </c>
       <c r="AE27" s="3">
         <v>7000</v>
       </c>
       <c r="AF27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AG27" s="3">
         <v>3300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>11700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>7900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>6200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3148,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3159,11 +3220,11 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
@@ -3174,29 +3235,29 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-100</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-200</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>5800</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3209,8 +3270,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3392,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,8 +3514,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3488,8 +3558,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3566,127 +3636,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E33" s="3">
         <v>5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>8700</v>
       </c>
       <c r="K33" s="3">
         <v>8700</v>
       </c>
       <c r="L33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="M33" s="3">
         <v>7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>11500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>9400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>7900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>6200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3880,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E35" s="3">
         <v>5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>8700</v>
       </c>
       <c r="K35" s="3">
         <v>8700</v>
       </c>
       <c r="L35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="M35" s="3">
         <v>7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>11500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>9400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>7900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>6200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E38" s="2">
         <v>46017</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45835</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45744</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45653</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45562</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45471</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45380</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45289</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45198</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44925</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44743</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44652</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44470</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44379</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44288</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44197</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44099</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44008</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43917</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43826</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43644</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43553</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43462</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43371</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43280</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43189</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43098</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43007</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42734</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4175,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,127 +4219,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E41" s="3">
         <v>18200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>67000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>47800</v>
       </c>
       <c r="S41" s="3">
         <v>47800</v>
       </c>
       <c r="T41" s="3">
+        <v>47800</v>
+      </c>
+      <c r="U41" s="3">
         <v>45800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>52900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>52500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>49500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>37400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>23300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>26000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>17500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>16200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>14400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>17100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>19700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4371,127 +4461,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>70300</v>
+      </c>
+      <c r="E43" s="3">
         <v>59500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>57300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>62600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>57100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>58000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>52100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>62200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>57800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>52000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>48400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>52100</v>
-      </c>
-      <c r="R43" s="3">
-        <v>50500</v>
       </c>
       <c r="S43" s="3">
         <v>50500</v>
       </c>
       <c r="T43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="U43" s="3">
         <v>50600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>49600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>47200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>38500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>32800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>36200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>37000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>53400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>49800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>57900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>54500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>56000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>54800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>56900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>56800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>51900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>52300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>55600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>50400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>49900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>47400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4531,8 +4627,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4609,8 +4705,11 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4650,205 +4749,211 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>5400</v>
       </c>
       <c r="S45" s="3">
         <v>5400</v>
       </c>
       <c r="T45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="U45" s="3">
         <v>5800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E46" s="3">
         <v>83900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>80400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>80200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>76300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>74900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>80300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>73700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>76800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>72000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>81200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>122400</v>
-      </c>
-      <c r="R46" s="3">
-        <v>103600</v>
       </c>
       <c r="S46" s="3">
         <v>103600</v>
       </c>
       <c r="T46" s="3">
+        <v>103600</v>
+      </c>
+      <c r="U46" s="3">
         <v>102200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>105700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>102300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>92400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>84800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>82700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>78100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>80000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>78600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>78000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>75300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>70700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>73100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>73800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>73300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>79100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>75300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>74700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>68000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>69600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>68800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4888,8 +4993,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4966,246 +5071,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E48" s="3">
         <v>26500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>19600</v>
       </c>
       <c r="S48" s="3">
         <v>19600</v>
       </c>
       <c r="T48" s="3">
-        <v>19700</v>
+        <v>19600</v>
       </c>
       <c r="U48" s="3">
         <v>19700</v>
       </c>
       <c r="V48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="W48" s="3">
         <v>19900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>28500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>29100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>29400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>28700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>28900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>24300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>22800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>20700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>18900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>17900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>16500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>15800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>14800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>93100</v>
+      </c>
+      <c r="E49" s="3">
         <v>93900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>94100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>95200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>92400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>92100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>92200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>84100</v>
       </c>
       <c r="K49" s="3">
         <v>84100</v>
       </c>
       <c r="L49" s="3">
+        <v>84100</v>
+      </c>
+      <c r="M49" s="3">
         <v>84200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>83700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>83800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>83500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>82500</v>
-      </c>
-      <c r="R49" s="3">
-        <v>84600</v>
       </c>
       <c r="S49" s="3">
         <v>84600</v>
       </c>
       <c r="T49" s="3">
-        <v>85100</v>
+        <v>84600</v>
       </c>
       <c r="U49" s="3">
         <v>85100</v>
       </c>
       <c r="V49" s="3">
-        <v>85400</v>
+        <v>85100</v>
       </c>
       <c r="W49" s="3">
         <v>85400</v>
       </c>
       <c r="X49" s="3">
+        <v>85400</v>
+      </c>
+      <c r="Y49" s="3">
         <v>85300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>83900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>83800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>83800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>84200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>84600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>84200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>84600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>84700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>85700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>85100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>85000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>85300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>72600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>72400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5437,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,8 +5559,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5469,7 +5589,7 @@
         <v>400</v>
       </c>
       <c r="K52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -5490,79 +5610,82 @@
         <v>300</v>
       </c>
       <c r="R52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="S52" s="3">
         <v>500</v>
       </c>
       <c r="T52" s="3">
+        <v>500</v>
+      </c>
+      <c r="U52" s="3">
         <v>600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5803,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>204400</v>
+      </c>
+      <c r="E54" s="3">
         <v>206400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>200700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>200500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>191800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>193300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>190800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>187500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>179300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>181400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>180800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>182900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>177700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>185000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>224700</v>
-      </c>
-      <c r="R54" s="3">
-        <v>208400</v>
       </c>
       <c r="S54" s="3">
         <v>208400</v>
       </c>
       <c r="T54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="U54" s="3">
         <v>207500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>211400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>208800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>199400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>192500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>196100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>192500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>195100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>193700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>193900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>191400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>187700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>180800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>187100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>185900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>191000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>185200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>182200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>174900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>160800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>159300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +5971,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,135 +6015,139 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
-      </c>
-      <c r="R57" s="3">
-        <v>8000</v>
       </c>
       <c r="S57" s="3">
         <v>8000</v>
       </c>
       <c r="T57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="U57" s="3">
         <v>7700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>7400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>11700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1200</v>
       </c>
       <c r="F58" s="3">
         <v>1200</v>
@@ -6022,31 +6156,31 @@
         <v>1200</v>
       </c>
       <c r="H58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1300</v>
-      </c>
-      <c r="N58" s="3">
-        <v>1200</v>
       </c>
       <c r="O58" s="3">
         <v>1200</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -6123,291 +6257,300 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E59" s="3">
         <v>18200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>50900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>47300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>39900</v>
       </c>
       <c r="S59" s="3">
         <v>39900</v>
       </c>
       <c r="T59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="U59" s="3">
         <v>47200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>50900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>41200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>36500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>40100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>37500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>30500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>35200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>34200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>35500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>30200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>36800</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>34100</v>
       </c>
       <c r="AH59" s="3">
         <v>34100</v>
       </c>
       <c r="AI59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>39800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>43000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>36000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>37100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>34200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>46700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E60" s="3">
         <v>48800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>42700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>49500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>46800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>44300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>49900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>47000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>59600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>51900</v>
-      </c>
-      <c r="R60" s="3">
-        <v>48000</v>
       </c>
       <c r="S60" s="3">
         <v>48000</v>
       </c>
       <c r="T60" s="3">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="U60" s="3">
         <v>54900</v>
       </c>
       <c r="V60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="W60" s="3">
         <v>55600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>46200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>42600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>45100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>42300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>43700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>39400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>42300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>36600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>44200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>39200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>42500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>48400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>51400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>44600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>45200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>45800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>55800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E61" s="3">
         <v>77000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>45300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>33300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>44500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>53800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>59100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>59700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6442,46 +6585,49 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>2500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13500</v>
-      </c>
-      <c r="AI61" s="3">
-        <v>19000</v>
       </c>
       <c r="AJ61" s="3">
         <v>19000</v>
       </c>
       <c r="AK61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AL61" s="3">
         <v>22000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>20000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>9000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>7000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6521,86 +6667,89 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>7500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8600</v>
-      </c>
-      <c r="R62" s="3">
-        <v>10200</v>
       </c>
       <c r="S62" s="3">
         <v>10200</v>
       </c>
       <c r="T62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="U62" s="3">
         <v>8800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>10000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>8300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>17500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>17800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>9900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>10200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +6867,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +6989,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7111,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>138400</v>
+      </c>
+      <c r="E66" s="3">
         <v>138300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>99000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>80700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>77300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>79800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>85300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>85800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>91300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>110000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>114200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>126700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60600</v>
-      </c>
-      <c r="R66" s="3">
-        <v>58100</v>
       </c>
       <c r="S66" s="3">
         <v>58100</v>
       </c>
       <c r="T66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="U66" s="3">
         <v>63700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>62900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>64400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>55900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>54300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>56100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>55200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>60200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>57900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>57200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>58700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>64300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>75700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>78000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>84100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>83100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>64700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>73000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>72200</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7279,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7399,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7521,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7643,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7765,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E72" s="3">
         <v>78400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>75800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>76500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>78100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>78300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>77800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>72200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>66500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>60800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>56000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>49500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31900</v>
-      </c>
-      <c r="R72" s="3">
-        <v>18300</v>
       </c>
       <c r="S72" s="3">
         <v>18300</v>
       </c>
       <c r="T72" s="3">
+        <v>18300</v>
+      </c>
+      <c r="U72" s="3">
         <v>11300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-14300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-17400</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-15200</v>
       </c>
       <c r="Z72" s="3">
         <v>-15200</v>
       </c>
       <c r="AA72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-13700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-18300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-25400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-19900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-25000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-31200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-38500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-43300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-48700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-56600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8009,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8131,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8253,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E76" s="3">
         <v>68100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>101600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>119800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>114400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>115600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>110900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>102200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>93500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>90100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>80800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>72900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>63400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>164100</v>
-      </c>
-      <c r="R76" s="3">
-        <v>150300</v>
       </c>
       <c r="S76" s="3">
         <v>150300</v>
       </c>
       <c r="T76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="U76" s="3">
         <v>143900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>148500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>144400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>143200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>140900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>138600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>136600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>140800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>137600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>138700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>131200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>129700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>123600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>128400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>121600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>115400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>107300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>98100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>91800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>96000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>86300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8497,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E80" s="2">
         <v>46017</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45835</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45744</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45653</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45562</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45471</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45380</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45289</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45198</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44925</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44743</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44652</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44470</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44379</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44288</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44197</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44099</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44008</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43917</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43826</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43644</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43553</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43462</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43371</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43280</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43189</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43098</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43007</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42734</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E81" s="3">
         <v>5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>8700</v>
       </c>
       <c r="K81" s="3">
         <v>8700</v>
       </c>
       <c r="L81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="M81" s="3">
         <v>7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>11500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>9400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>7900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>6200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,13 +8792,14 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
         <v>900</v>
@@ -8618,7 +8817,7 @@
         <v>900</v>
       </c>
       <c r="J83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
@@ -8642,16 +8841,16 @@
         <v>800</v>
       </c>
       <c r="R83" s="3">
+        <v>800</v>
+      </c>
+      <c r="S83" s="3">
         <v>1800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1100</v>
       </c>
       <c r="V83" s="3">
         <v>1100</v>
@@ -8660,19 +8859,19 @@
         <v>1100</v>
       </c>
       <c r="X83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Y83" s="3">
         <v>1200</v>
       </c>
       <c r="Z83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>1100</v>
       </c>
       <c r="AC83" s="3">
         <v>1100</v>
@@ -8681,10 +8880,10 @@
         <v>1100</v>
       </c>
       <c r="AE83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF83" s="3">
         <v>900</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>1200</v>
       </c>
       <c r="AG83" s="3">
         <v>1200</v>
@@ -8699,22 +8898,25 @@
         <v>1200</v>
       </c>
       <c r="AK83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="AL83" s="3">
         <v>1100</v>
       </c>
       <c r="AM83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AN83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>900</v>
       </c>
       <c r="AO83" s="3">
         <v>900</v>
       </c>
+      <c r="AP83" s="3">
+        <v>900</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9034,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9156,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9278,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9400,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9522,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>19100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>24800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>24300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>19900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>13800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>15800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>9500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>10000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>4900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>12100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,31 +9690,32 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-900</v>
       </c>
       <c r="K91" s="3">
         <v>-900</v>
@@ -9503,7 +9724,7 @@
         <v>-900</v>
       </c>
       <c r="M91" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="N91" s="3">
         <v>-1100</v>
@@ -9512,13 +9733,13 @@
         <v>-1100</v>
       </c>
       <c r="P91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-900</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-1000</v>
       </c>
       <c r="S91" s="3">
         <v>-1000</v>
@@ -9527,70 +9748,73 @@
         <v>-1000</v>
       </c>
       <c r="U91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +9932,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,31 +10054,34 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7800</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-900</v>
       </c>
       <c r="K94" s="3">
         <v>-900</v>
@@ -9860,7 +10090,7 @@
         <v>-900</v>
       </c>
       <c r="M94" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="N94" s="3">
         <v>-1100</v>
@@ -9869,85 +10099,88 @@
         <v>-1100</v>
       </c>
       <c r="P94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2300</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-1000</v>
       </c>
       <c r="T94" s="3">
         <v>-1000</v>
       </c>
       <c r="U94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-10300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,13 +10222,14 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="E96" s="3">
         <v>3300</v>
@@ -10004,7 +10238,7 @@
         <v>3300</v>
       </c>
       <c r="G96" s="3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="H96" s="3">
         <v>3000</v>
@@ -10031,7 +10265,7 @@
         <v>3000</v>
       </c>
       <c r="P96" s="3">
-        <v>-3500</v>
+        <v>3000</v>
       </c>
       <c r="Q96" s="3">
         <v>-3500</v>
@@ -10040,76 +10274,79 @@
         <v>-3500</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-6400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-3200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-4600</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10464,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10586,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,132 +10708,138 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-26000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>3600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -10659,35 +10908,35 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
         <v>0</v>
       </c>
@@ -10703,123 +10952,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E102" s="3">
         <v>4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>5400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1300</v>
       </c>
     </row>
